--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614078</v>
+        <v>118614088</v>
       </c>
       <c r="B7" t="n">
-        <v>79102</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455889</v>
+        <v>455935</v>
       </c>
       <c r="R7" t="n">
-        <v>6836903</v>
+        <v>6836858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118614088</v>
+        <v>118614078</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>79102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455935</v>
+        <v>455889</v>
       </c>
       <c r="R8" t="n">
-        <v>6836858</v>
+        <v>6836903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118614084</v>
+        <v>118614083</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456032</v>
+        <v>455947</v>
       </c>
       <c r="R9" t="n">
-        <v>6836895</v>
+        <v>6837045</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118614083</v>
+        <v>118614084</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455947</v>
+        <v>456032</v>
       </c>
       <c r="R10" t="n">
-        <v>6837045</v>
+        <v>6836895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118727619</v>
+        <v>118727538</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4070,34 +4070,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455726</v>
+        <v>456041</v>
       </c>
       <c r="R35" t="n">
-        <v>6837099</v>
+        <v>6836794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4156,10 +4157,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118727637</v>
+        <v>118727600</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>80441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4172,21 +4173,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4196,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455922</v>
+        <v>455702</v>
       </c>
       <c r="R36" t="n">
-        <v>6836913</v>
+        <v>6837084</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,10 +4259,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118727538</v>
+        <v>118727619</v>
       </c>
       <c r="B37" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4274,35 +4275,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456041</v>
+        <v>455726</v>
       </c>
       <c r="R37" t="n">
-        <v>6836794</v>
+        <v>6837099</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118727600</v>
+        <v>118727637</v>
       </c>
       <c r="B38" t="n">
-        <v>80441</v>
+        <v>78484</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455702</v>
+        <v>455922</v>
       </c>
       <c r="R38" t="n">
-        <v>6837084</v>
+        <v>6836913</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727612</v>
+        <v>118727545</v>
       </c>
       <c r="B69" t="n">
-        <v>90654</v>
+        <v>79073</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7558,38 +7558,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455930</v>
+        <v>455700</v>
       </c>
       <c r="R69" t="n">
-        <v>6836843</v>
+        <v>6837083</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7648,10 +7649,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727624</v>
+        <v>118727612</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>90654</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7660,25 +7661,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7688,10 +7689,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455844</v>
+        <v>455930</v>
       </c>
       <c r="R70" t="n">
-        <v>6837118</v>
+        <v>6836843</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7750,7 +7751,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727631</v>
+        <v>118727624</v>
       </c>
       <c r="B71" t="n">
         <v>78484</v>
@@ -7790,10 +7791,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455914</v>
+        <v>455844</v>
       </c>
       <c r="R71" t="n">
-        <v>6836965</v>
+        <v>6837118</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,10 +7853,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727508</v>
+        <v>118727631</v>
       </c>
       <c r="B72" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7868,35 +7869,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455765</v>
+        <v>455914</v>
       </c>
       <c r="R72" t="n">
-        <v>6837108</v>
+        <v>6836965</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727545</v>
+        <v>118727508</v>
       </c>
       <c r="B73" t="n">
-        <v>79073</v>
+        <v>78518</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7971,21 +7971,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455700</v>
+        <v>455765</v>
       </c>
       <c r="R73" t="n">
-        <v>6837083</v>
+        <v>6837108</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118727665</v>
+        <v>118727596</v>
       </c>
       <c r="B75" t="n">
-        <v>77868</v>
+        <v>78221</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8177,21 +8177,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455701</v>
+        <v>455956</v>
       </c>
       <c r="R75" t="n">
-        <v>6837084</v>
+        <v>6837009</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118727618</v>
+        <v>118727586</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455724</v>
+        <v>455865</v>
       </c>
       <c r="R76" t="n">
-        <v>6837080</v>
+        <v>6836943</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118727513</v>
+        <v>118727665</v>
       </c>
       <c r="B77" t="n">
-        <v>78518</v>
+        <v>77868</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8381,35 +8381,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>455971</v>
+        <v>455701</v>
       </c>
       <c r="R77" t="n">
-        <v>6836747</v>
+        <v>6837084</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,10 +8569,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118727608</v>
+        <v>118727618</v>
       </c>
       <c r="B79" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8586,21 +8585,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8610,10 +8609,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456041</v>
+        <v>455724</v>
       </c>
       <c r="R79" t="n">
-        <v>6836795</v>
+        <v>6837080</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8672,10 +8671,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118727596</v>
+        <v>118727513</v>
       </c>
       <c r="B80" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,34 +8687,35 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455956</v>
+        <v>455971</v>
       </c>
       <c r="R80" t="n">
-        <v>6837009</v>
+        <v>6836747</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8774,10 +8774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118727586</v>
+        <v>118727608</v>
       </c>
       <c r="B81" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8790,21 +8790,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455865</v>
+        <v>456041</v>
       </c>
       <c r="R81" t="n">
-        <v>6836943</v>
+        <v>6836795</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9389,10 +9389,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727609</v>
+        <v>118727506</v>
       </c>
       <c r="B87" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9405,34 +9405,35 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456053</v>
+        <v>455726</v>
       </c>
       <c r="R87" t="n">
-        <v>6836858</v>
+        <v>6837083</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9491,10 +9492,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727531</v>
+        <v>118727609</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9507,35 +9508,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455918</v>
+        <v>456053</v>
       </c>
       <c r="R88" t="n">
-        <v>6836750</v>
+        <v>6836858</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9594,7 +9594,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118727543</v>
+        <v>118727531</v>
       </c>
       <c r="B89" t="n">
         <v>79102</v>
@@ -9635,10 +9635,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456050</v>
+        <v>455918</v>
       </c>
       <c r="R89" t="n">
-        <v>6836858</v>
+        <v>6836750</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9697,10 +9697,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118727506</v>
+        <v>118727543</v>
       </c>
       <c r="B90" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9713,21 +9713,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455726</v>
+        <v>456050</v>
       </c>
       <c r="R90" t="n">
-        <v>6837083</v>
+        <v>6836858</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10310,10 +10310,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118727584</v>
+        <v>118727560</v>
       </c>
       <c r="B96" t="n">
-        <v>78221</v>
+        <v>78583</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10326,34 +10326,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456053</v>
+        <v>455904</v>
       </c>
       <c r="R96" t="n">
-        <v>6836858</v>
+        <v>6836777</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10394,6 +10405,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10412,10 +10424,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118727560</v>
+        <v>118727638</v>
       </c>
       <c r="B97" t="n">
-        <v>78583</v>
+        <v>78484</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10428,45 +10440,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455904</v>
+        <v>455933</v>
       </c>
       <c r="R97" t="n">
-        <v>6836777</v>
+        <v>6836917</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10507,7 +10508,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10526,10 +10526,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118727638</v>
+        <v>118727529</v>
       </c>
       <c r="B98" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10542,34 +10542,35 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455933</v>
+        <v>455885</v>
       </c>
       <c r="R98" t="n">
-        <v>6836917</v>
+        <v>6836757</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10628,10 +10629,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118727529</v>
+        <v>118727662</v>
       </c>
       <c r="B99" t="n">
-        <v>79102</v>
+        <v>77416</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10644,35 +10645,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455885</v>
+        <v>455700</v>
       </c>
       <c r="R99" t="n">
-        <v>6836757</v>
+        <v>6837084</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10731,10 +10731,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118727662</v>
+        <v>118727584</v>
       </c>
       <c r="B100" t="n">
-        <v>77416</v>
+        <v>78221</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10747,21 +10747,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455700</v>
+        <v>456053</v>
       </c>
       <c r="R100" t="n">
-        <v>6837084</v>
+        <v>6836858</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727599</v>
+        <v>118727585</v>
       </c>
       <c r="B111" t="n">
-        <v>90966</v>
+        <v>78221</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11884,21 +11884,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5467</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455957</v>
+        <v>455930</v>
       </c>
       <c r="R111" t="n">
-        <v>6836745</v>
+        <v>6836897</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727582</v>
+        <v>118727660</v>
       </c>
       <c r="B112" t="n">
-        <v>57290</v>
+        <v>78129</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11986,42 +11986,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455915</v>
+        <v>456065</v>
       </c>
       <c r="R112" t="n">
-        <v>6836954</v>
+        <v>6836867</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12054,11 +12046,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,10 +12072,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727660</v>
+        <v>118727607</v>
       </c>
       <c r="B113" t="n">
-        <v>78129</v>
+        <v>78220</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12101,21 +12088,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12125,10 +12112,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456065</v>
+        <v>456027</v>
       </c>
       <c r="R113" t="n">
-        <v>6836867</v>
+        <v>6836806</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12187,10 +12174,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727607</v>
+        <v>118727599</v>
       </c>
       <c r="B114" t="n">
-        <v>78220</v>
+        <v>90966</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12203,21 +12190,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>5467</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12227,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456027</v>
+        <v>455957</v>
       </c>
       <c r="R114" t="n">
-        <v>6836806</v>
+        <v>6836745</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12289,10 +12276,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727585</v>
+        <v>118727582</v>
       </c>
       <c r="B115" t="n">
-        <v>78221</v>
+        <v>57290</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12305,34 +12292,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455930</v>
+        <v>455915</v>
       </c>
       <c r="R115" t="n">
-        <v>6836897</v>
+        <v>6836954</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12365,6 +12360,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -4565,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727668</v>
+        <v>118727625</v>
       </c>
       <c r="B40" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456028</v>
+        <v>455868</v>
       </c>
       <c r="R40" t="n">
-        <v>6836814</v>
+        <v>6837146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727511</v>
+        <v>118727668</v>
       </c>
       <c r="B41" t="n">
-        <v>78518</v>
+        <v>77868</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4683,35 +4683,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455951</v>
+        <v>456028</v>
       </c>
       <c r="R41" t="n">
-        <v>6836741</v>
+        <v>6836814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4769,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727520</v>
+        <v>118727617</v>
       </c>
       <c r="B42" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,35 +4785,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455867</v>
+        <v>455720</v>
       </c>
       <c r="R42" t="n">
-        <v>6836942</v>
+        <v>6837077</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,10 +4871,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727528</v>
+        <v>118727622</v>
       </c>
       <c r="B43" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4889,35 +4887,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455898</v>
+        <v>455747</v>
       </c>
       <c r="R43" t="n">
-        <v>6836767</v>
+        <v>6837101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,7 +4973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727625</v>
+        <v>118727636</v>
       </c>
       <c r="B44" t="n">
         <v>78484</v>
@@ -5016,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455868</v>
+        <v>455925</v>
       </c>
       <c r="R44" t="n">
-        <v>6837146</v>
+        <v>6836919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5078,10 +5075,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727617</v>
+        <v>118727511</v>
       </c>
       <c r="B45" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5094,34 +5091,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455720</v>
+        <v>455951</v>
       </c>
       <c r="R45" t="n">
-        <v>6837077</v>
+        <v>6836741</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5180,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727622</v>
+        <v>118727520</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5196,34 +5194,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455747</v>
+        <v>455867</v>
       </c>
       <c r="R46" t="n">
-        <v>6837101</v>
+        <v>6836942</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727636</v>
+        <v>118727528</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5298,34 +5297,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455925</v>
+        <v>455898</v>
       </c>
       <c r="R47" t="n">
-        <v>6836919</v>
+        <v>6836767</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727545</v>
+        <v>118727624</v>
       </c>
       <c r="B69" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7562,35 +7562,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455700</v>
+        <v>455844</v>
       </c>
       <c r="R69" t="n">
-        <v>6837083</v>
+        <v>6837118</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7649,10 +7648,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727612</v>
+        <v>118727631</v>
       </c>
       <c r="B70" t="n">
-        <v>90654</v>
+        <v>78484</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7661,25 +7660,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7689,10 +7688,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455930</v>
+        <v>455914</v>
       </c>
       <c r="R70" t="n">
-        <v>6836843</v>
+        <v>6836965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7751,10 +7750,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727624</v>
+        <v>118727549</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7767,34 +7766,35 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455844</v>
+        <v>455956</v>
       </c>
       <c r="R71" t="n">
-        <v>6837118</v>
+        <v>6836745</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7853,10 +7853,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727631</v>
+        <v>118727545</v>
       </c>
       <c r="B72" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7869,34 +7869,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455914</v>
+        <v>455700</v>
       </c>
       <c r="R72" t="n">
-        <v>6836965</v>
+        <v>6837083</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7955,10 +7956,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727508</v>
+        <v>118727612</v>
       </c>
       <c r="B73" t="n">
-        <v>78518</v>
+        <v>90654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7967,39 +7968,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455765</v>
+        <v>455930</v>
       </c>
       <c r="R73" t="n">
-        <v>6837108</v>
+        <v>6836843</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8058,10 +8058,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118727549</v>
+        <v>118727508</v>
       </c>
       <c r="B74" t="n">
-        <v>79073</v>
+        <v>78518</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8074,21 +8074,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455956</v>
+        <v>455765</v>
       </c>
       <c r="R74" t="n">
-        <v>6836745</v>
+        <v>6837108</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8876,10 +8876,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118727547</v>
+        <v>118727541</v>
       </c>
       <c r="B82" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8892,21 +8892,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8917,10 +8917,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>455904</v>
+        <v>456048</v>
       </c>
       <c r="R82" t="n">
-        <v>6836778</v>
+        <v>6836813</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8979,7 +8979,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118727541</v>
+        <v>118727525</v>
       </c>
       <c r="B83" t="n">
         <v>79102</v>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456048</v>
+        <v>455924</v>
       </c>
       <c r="R83" t="n">
-        <v>6836813</v>
+        <v>6836801</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118727525</v>
+        <v>118727547</v>
       </c>
       <c r="B84" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9098,21 +9098,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>455924</v>
+        <v>455904</v>
       </c>
       <c r="R84" t="n">
-        <v>6836801</v>
+        <v>6836778</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11548,10 +11548,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118727558</v>
+        <v>118727550</v>
       </c>
       <c r="B108" t="n">
-        <v>78583</v>
+        <v>79073</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11564,45 +11564,35 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>456036</v>
+        <v>455970</v>
       </c>
       <c r="R108" t="n">
-        <v>6836794</v>
+        <v>6836763</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11643,7 +11633,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11765,10 +11754,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727550</v>
+        <v>118727558</v>
       </c>
       <c r="B110" t="n">
-        <v>79073</v>
+        <v>78583</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11781,35 +11770,45 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>455970</v>
+        <v>456036</v>
       </c>
       <c r="R110" t="n">
-        <v>6836763</v>
+        <v>6836794</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11850,6 +11849,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727585</v>
+        <v>118727599</v>
       </c>
       <c r="B111" t="n">
-        <v>78221</v>
+        <v>90966</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11884,21 +11884,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>5467</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455930</v>
+        <v>455957</v>
       </c>
       <c r="R111" t="n">
-        <v>6836897</v>
+        <v>6836745</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727660</v>
+        <v>118727582</v>
       </c>
       <c r="B112" t="n">
-        <v>78129</v>
+        <v>57290</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11986,34 +11986,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456065</v>
+        <v>455915</v>
       </c>
       <c r="R112" t="n">
-        <v>6836867</v>
+        <v>6836954</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12046,6 +12054,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12072,10 +12085,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727607</v>
+        <v>118727660</v>
       </c>
       <c r="B113" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12088,21 +12101,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12112,10 +12125,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456027</v>
+        <v>456065</v>
       </c>
       <c r="R113" t="n">
-        <v>6836806</v>
+        <v>6836867</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,10 +12187,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727599</v>
+        <v>118727607</v>
       </c>
       <c r="B114" t="n">
-        <v>90966</v>
+        <v>78220</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12190,21 +12203,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5467</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12214,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455957</v>
+        <v>456027</v>
       </c>
       <c r="R114" t="n">
-        <v>6836745</v>
+        <v>6836806</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12276,10 +12289,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727582</v>
+        <v>118727585</v>
       </c>
       <c r="B115" t="n">
-        <v>57290</v>
+        <v>78221</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12292,42 +12305,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455915</v>
+        <v>455930</v>
       </c>
       <c r="R115" t="n">
-        <v>6836954</v>
+        <v>6836897</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12360,11 +12365,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12391,10 +12391,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727557</v>
+        <v>118727633</v>
       </c>
       <c r="B116" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12407,35 +12407,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>456053</v>
+        <v>455917</v>
       </c>
       <c r="R116" t="n">
-        <v>6836858</v>
+        <v>6836957</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12494,10 +12493,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727633</v>
+        <v>118727557</v>
       </c>
       <c r="B117" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12510,34 +12509,35 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455917</v>
+        <v>456053</v>
       </c>
       <c r="R117" t="n">
-        <v>6836957</v>
+        <v>6836858</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12596,10 +12596,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727542</v>
+        <v>118727548</v>
       </c>
       <c r="B118" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12612,21 +12612,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12637,10 +12637,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>456022</v>
+        <v>455926</v>
       </c>
       <c r="R118" t="n">
-        <v>6836819</v>
+        <v>6836752</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12699,7 +12699,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727518</v>
+        <v>118727542</v>
       </c>
       <c r="B119" t="n">
         <v>79102</v>
@@ -12740,10 +12740,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455952</v>
+        <v>456022</v>
       </c>
       <c r="R119" t="n">
-        <v>6836992</v>
+        <v>6836819</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727548</v>
+        <v>118727518</v>
       </c>
       <c r="B120" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12818,21 +12818,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12843,10 +12843,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455926</v>
+        <v>455952</v>
       </c>
       <c r="R120" t="n">
-        <v>6836752</v>
+        <v>6836992</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118614110</v>
+        <v>118614079</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456021</v>
+        <v>455886</v>
       </c>
       <c r="R2" t="n">
-        <v>6836968</v>
+        <v>6836900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118614108</v>
+        <v>118614081</v>
       </c>
       <c r="B3" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455960</v>
+        <v>455942</v>
       </c>
       <c r="R3" t="n">
-        <v>6837047</v>
+        <v>6837031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118614095</v>
+        <v>118614111</v>
       </c>
       <c r="B4" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455985</v>
+        <v>455971</v>
       </c>
       <c r="R4" t="n">
-        <v>6836979</v>
+        <v>6837047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118614076</v>
+        <v>118614087</v>
       </c>
       <c r="B5" t="n">
-        <v>78518</v>
+        <v>78583</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456018</v>
+        <v>455959</v>
       </c>
       <c r="R5" t="n">
-        <v>6837020</v>
+        <v>6837052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614109</v>
+        <v>118614103</v>
       </c>
       <c r="B6" t="n">
         <v>78220</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456008</v>
+        <v>455886</v>
       </c>
       <c r="R6" t="n">
-        <v>6837047</v>
+        <v>6836900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614088</v>
+        <v>118614110</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455935</v>
+        <v>456021</v>
       </c>
       <c r="R7" t="n">
-        <v>6836858</v>
+        <v>6836968</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118614078</v>
+        <v>118614089</v>
       </c>
       <c r="B8" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455889</v>
+        <v>456021</v>
       </c>
       <c r="R8" t="n">
-        <v>6836903</v>
+        <v>6837003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1371,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118614083</v>
+        <v>118614093</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455947</v>
+        <v>456008</v>
       </c>
       <c r="R9" t="n">
-        <v>6837045</v>
+        <v>6837047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118614084</v>
+        <v>118614092</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1520,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456032</v>
+        <v>455960</v>
       </c>
       <c r="R10" t="n">
-        <v>6836895</v>
+        <v>6837047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118614096</v>
+        <v>118614086</v>
       </c>
       <c r="B11" t="n">
-        <v>78220</v>
+        <v>78583</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456010</v>
+        <v>455907</v>
       </c>
       <c r="R11" t="n">
-        <v>6836965</v>
+        <v>6837012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118614103</v>
+        <v>118614078</v>
       </c>
       <c r="B12" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1724,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455886</v>
+        <v>455889</v>
       </c>
       <c r="R12" t="n">
-        <v>6836900</v>
+        <v>6836903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118614079</v>
+        <v>118614098</v>
       </c>
       <c r="B13" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455886</v>
+        <v>455984</v>
       </c>
       <c r="R13" t="n">
-        <v>6836900</v>
+        <v>6836875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118614107</v>
+        <v>118614109</v>
       </c>
       <c r="B14" t="n">
         <v>78220</v>
@@ -1939,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455942</v>
+        <v>456008</v>
       </c>
       <c r="R14" t="n">
-        <v>6836999</v>
+        <v>6837047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118614086</v>
+        <v>118614096</v>
       </c>
       <c r="B15" t="n">
-        <v>78583</v>
+        <v>78220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455907</v>
+        <v>456010</v>
       </c>
       <c r="R15" t="n">
-        <v>6837012</v>
+        <v>6836965</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118614082</v>
+        <v>118614084</v>
       </c>
       <c r="B16" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455942</v>
+        <v>456032</v>
       </c>
       <c r="R16" t="n">
-        <v>6837052</v>
+        <v>6836895</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118614081</v>
+        <v>118614097</v>
       </c>
       <c r="B17" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2234,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455942</v>
+        <v>456025</v>
       </c>
       <c r="R17" t="n">
-        <v>6837031</v>
+        <v>6836910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2320,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118614105</v>
+        <v>118614102</v>
       </c>
       <c r="B18" t="n">
         <v>78220</v>
@@ -2347,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455881</v>
+        <v>455889</v>
       </c>
       <c r="R18" t="n">
-        <v>6836923</v>
+        <v>6836903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118614102</v>
+        <v>118614076</v>
       </c>
       <c r="B19" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455889</v>
+        <v>456018</v>
       </c>
       <c r="R19" t="n">
-        <v>6836903</v>
+        <v>6837020</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2524,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118614100</v>
+        <v>118614107</v>
       </c>
       <c r="B20" t="n">
         <v>78220</v>
@@ -2551,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455939</v>
+        <v>455942</v>
       </c>
       <c r="R20" t="n">
-        <v>6836859</v>
+        <v>6836999</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118614111</v>
+        <v>118614083</v>
       </c>
       <c r="B21" t="n">
-        <v>78129</v>
+        <v>79102</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2642,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455971</v>
+        <v>455947</v>
       </c>
       <c r="R21" t="n">
-        <v>6837047</v>
+        <v>6837045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2728,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118614087</v>
+        <v>118614082</v>
       </c>
       <c r="B22" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2744,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,7 +2768,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455959</v>
+        <v>455942</v>
       </c>
       <c r="R22" t="n">
         <v>6837052</v>
@@ -2817,7 +2830,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118614106</v>
+        <v>118614104</v>
       </c>
       <c r="B23" t="n">
         <v>78220</v>
@@ -2857,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455886</v>
+        <v>455867</v>
       </c>
       <c r="R23" t="n">
-        <v>6836975</v>
+        <v>6836907</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2932,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118614090</v>
+        <v>118614105</v>
       </c>
       <c r="B24" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455935</v>
+        <v>455881</v>
       </c>
       <c r="R24" t="n">
-        <v>6836857</v>
+        <v>6836923</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118614104</v>
+        <v>118614077</v>
       </c>
       <c r="B25" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3050,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455867</v>
+        <v>456008</v>
       </c>
       <c r="R25" t="n">
-        <v>6836907</v>
+        <v>6836969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118614077</v>
+        <v>118614101</v>
       </c>
       <c r="B26" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3152,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456008</v>
+        <v>455923</v>
       </c>
       <c r="R26" t="n">
-        <v>6836969</v>
+        <v>6836875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3238,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118614097</v>
+        <v>118614099</v>
       </c>
       <c r="B27" t="n">
         <v>78220</v>
@@ -3265,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456025</v>
+        <v>455969</v>
       </c>
       <c r="R27" t="n">
-        <v>6836910</v>
+        <v>6836868</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3340,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118614101</v>
+        <v>118614090</v>
       </c>
       <c r="B28" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3356,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455923</v>
+        <v>455935</v>
       </c>
       <c r="R28" t="n">
-        <v>6836875</v>
+        <v>6836857</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118614092</v>
+        <v>118614088</v>
       </c>
       <c r="B29" t="n">
-        <v>78221</v>
+        <v>57443</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3458,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455960</v>
+        <v>455935</v>
       </c>
       <c r="R29" t="n">
-        <v>6837047</v>
+        <v>6836858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3544,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118614098</v>
+        <v>118614095</v>
       </c>
       <c r="B30" t="n">
         <v>78220</v>
@@ -3571,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455984</v>
+        <v>455985</v>
       </c>
       <c r="R30" t="n">
-        <v>6836875</v>
+        <v>6836979</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3646,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118614091</v>
+        <v>118614108</v>
       </c>
       <c r="B31" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3662,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455881</v>
+        <v>455960</v>
       </c>
       <c r="R31" t="n">
-        <v>6836923</v>
+        <v>6837047</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3748,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118614099</v>
+        <v>118614100</v>
       </c>
       <c r="B32" t="n">
         <v>78220</v>
@@ -3775,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455969</v>
+        <v>455939</v>
       </c>
       <c r="R32" t="n">
-        <v>6836868</v>
+        <v>6836859</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118614089</v>
+        <v>118614091</v>
       </c>
       <c r="B33" t="n">
-        <v>57290</v>
+        <v>78221</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,42 +3866,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456021</v>
+        <v>455881</v>
       </c>
       <c r="R33" t="n">
-        <v>6837003</v>
+        <v>6836923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3921,11 +3926,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3952,10 +3952,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118614093</v>
+        <v>118614106</v>
       </c>
       <c r="B34" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456008</v>
+        <v>455886</v>
       </c>
       <c r="R34" t="n">
-        <v>6837047</v>
+        <v>6836975</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118727538</v>
+        <v>118727558</v>
       </c>
       <c r="B35" t="n">
-        <v>79102</v>
+        <v>78583</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4070,32 +4070,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456041</v>
+        <v>456036</v>
       </c>
       <c r="R35" t="n">
         <v>6836794</v>
@@ -4139,6 +4149,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4157,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118727600</v>
+        <v>118727633</v>
       </c>
       <c r="B36" t="n">
-        <v>80441</v>
+        <v>78484</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4173,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4197,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455702</v>
+        <v>455917</v>
       </c>
       <c r="R36" t="n">
-        <v>6837084</v>
+        <v>6836957</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118727619</v>
+        <v>118727608</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4275,21 +4286,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4299,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455726</v>
+        <v>456041</v>
       </c>
       <c r="R37" t="n">
-        <v>6837099</v>
+        <v>6836795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118727637</v>
+        <v>118727581</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4377,34 +4388,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455922</v>
+        <v>455926</v>
       </c>
       <c r="R38" t="n">
-        <v>6836913</v>
+        <v>6836949</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4463,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118727590</v>
+        <v>118727609</v>
       </c>
       <c r="B39" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4479,21 +4503,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4503,10 +4527,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455955</v>
+        <v>456053</v>
       </c>
       <c r="R39" t="n">
-        <v>6836833</v>
+        <v>6836858</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4565,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727625</v>
+        <v>118727612</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>90654</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,25 +4601,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4605,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455868</v>
+        <v>455930</v>
       </c>
       <c r="R40" t="n">
-        <v>6837146</v>
+        <v>6836843</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727668</v>
+        <v>118727625</v>
       </c>
       <c r="B41" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4683,21 +4707,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456028</v>
+        <v>455868</v>
       </c>
       <c r="R41" t="n">
-        <v>6836814</v>
+        <v>6837146</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4793,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727617</v>
+        <v>118727529</v>
       </c>
       <c r="B42" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4785,34 +4809,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455720</v>
+        <v>455885</v>
       </c>
       <c r="R42" t="n">
-        <v>6837077</v>
+        <v>6836757</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727622</v>
+        <v>118727520</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4887,34 +4912,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455747</v>
+        <v>455867</v>
       </c>
       <c r="R43" t="n">
-        <v>6837101</v>
+        <v>6836942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727636</v>
+        <v>118727537</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4989,34 +5015,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455925</v>
+        <v>456027</v>
       </c>
       <c r="R44" t="n">
-        <v>6836919</v>
+        <v>6836806</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,7 +5102,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727511</v>
+        <v>118727506</v>
       </c>
       <c r="B45" t="n">
         <v>78518</v>
@@ -5116,10 +5143,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455951</v>
+        <v>455726</v>
       </c>
       <c r="R45" t="n">
-        <v>6836741</v>
+        <v>6837083</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,10 +5205,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727520</v>
+        <v>118727655</v>
       </c>
       <c r="B46" t="n">
-        <v>79102</v>
+        <v>78129</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5194,35 +5221,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455867</v>
+        <v>455973</v>
       </c>
       <c r="R46" t="n">
-        <v>6836942</v>
+        <v>6836775</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,10 +5307,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727528</v>
+        <v>118727648</v>
       </c>
       <c r="B47" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,35 +5323,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455898</v>
+        <v>456055</v>
       </c>
       <c r="R47" t="n">
-        <v>6836767</v>
+        <v>6836875</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,10 +5409,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118727517</v>
+        <v>118727549</v>
       </c>
       <c r="B48" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5400,21 +5425,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5425,10 +5450,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455986</v>
+        <v>455956</v>
       </c>
       <c r="R48" t="n">
-        <v>6836980</v>
+        <v>6836745</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5487,10 +5512,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118727553</v>
+        <v>118727587</v>
       </c>
       <c r="B49" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5503,35 +5528,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456026</v>
+        <v>455933</v>
       </c>
       <c r="R49" t="n">
-        <v>6836798</v>
+        <v>6836859</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5590,10 +5614,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118727648</v>
+        <v>118727547</v>
       </c>
       <c r="B50" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5606,34 +5630,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456055</v>
+        <v>455904</v>
       </c>
       <c r="R50" t="n">
-        <v>6836875</v>
+        <v>6836778</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118727651</v>
+        <v>118727511</v>
       </c>
       <c r="B51" t="n">
-        <v>90749</v>
+        <v>78518</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5704,38 +5729,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455972</v>
+        <v>455951</v>
       </c>
       <c r="R51" t="n">
-        <v>6836775</v>
+        <v>6836741</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5794,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118727610</v>
+        <v>118727620</v>
       </c>
       <c r="B52" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5810,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5834,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455955</v>
+        <v>455733</v>
       </c>
       <c r="R52" t="n">
-        <v>6837009</v>
+        <v>6837103</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,10 +5922,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118727523</v>
+        <v>118727653</v>
       </c>
       <c r="B53" t="n">
-        <v>79102</v>
+        <v>94513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5908,39 +5934,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455933</v>
+        <v>456022</v>
       </c>
       <c r="R53" t="n">
-        <v>6836859</v>
+        <v>6836970</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118727556</v>
+        <v>118727638</v>
       </c>
       <c r="B54" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,35 +6040,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456028</v>
+        <v>455933</v>
       </c>
       <c r="R54" t="n">
-        <v>6836813</v>
+        <v>6836917</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6102,10 +6126,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118727653</v>
+        <v>118727541</v>
       </c>
       <c r="B55" t="n">
-        <v>94513</v>
+        <v>79102</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6114,38 +6138,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456022</v>
+        <v>456048</v>
       </c>
       <c r="R55" t="n">
-        <v>6836970</v>
+        <v>6836813</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6204,10 +6229,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118727562</v>
+        <v>118727528</v>
       </c>
       <c r="B56" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6220,34 +6245,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455956</v>
+        <v>455898</v>
       </c>
       <c r="R56" t="n">
-        <v>6836833</v>
+        <v>6836767</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6306,10 +6332,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118727640</v>
+        <v>118727538</v>
       </c>
       <c r="B57" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6322,34 +6348,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455987</v>
+        <v>456041</v>
       </c>
       <c r="R57" t="n">
-        <v>6836765</v>
+        <v>6836794</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,10 +6435,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118727639</v>
+        <v>118727603</v>
       </c>
       <c r="B58" t="n">
-        <v>78484</v>
+        <v>80441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6424,21 +6451,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6448,10 +6475,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455967</v>
+        <v>456024</v>
       </c>
       <c r="R58" t="n">
-        <v>6836746</v>
+        <v>6836818</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,7 +6537,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118727627</v>
+        <v>118727617</v>
       </c>
       <c r="B59" t="n">
         <v>78484</v>
@@ -6550,10 +6577,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455891</v>
+        <v>455720</v>
       </c>
       <c r="R59" t="n">
-        <v>6836950</v>
+        <v>6837077</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6612,10 +6639,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118727579</v>
+        <v>118727665</v>
       </c>
       <c r="B60" t="n">
-        <v>78573</v>
+        <v>77868</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6624,25 +6651,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6450</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6652,10 +6679,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455885</v>
+        <v>455701</v>
       </c>
       <c r="R60" t="n">
-        <v>6836936</v>
+        <v>6837084</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6714,10 +6741,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118727664</v>
+        <v>118727619</v>
       </c>
       <c r="B61" t="n">
-        <v>77416</v>
+        <v>78484</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6730,21 +6757,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6754,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456028</v>
+        <v>455726</v>
       </c>
       <c r="R61" t="n">
-        <v>6836814</v>
+        <v>6837099</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6816,10 +6843,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118727533</v>
+        <v>118727582</v>
       </c>
       <c r="B62" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6832,35 +6859,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455956</v>
+        <v>455915</v>
       </c>
       <c r="R62" t="n">
-        <v>6836745</v>
+        <v>6836954</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6893,6 +6927,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6919,10 +6958,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118727581</v>
+        <v>118727545</v>
       </c>
       <c r="B63" t="n">
-        <v>57290</v>
+        <v>79073</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6935,42 +6974,35 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455926</v>
+        <v>455700</v>
       </c>
       <c r="R63" t="n">
-        <v>6836949</v>
+        <v>6837083</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7003,11 +7035,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7034,10 +7061,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118727667</v>
+        <v>118727556</v>
       </c>
       <c r="B64" t="n">
-        <v>77868</v>
+        <v>79073</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7050,34 +7077,35 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456035</v>
+        <v>456028</v>
       </c>
       <c r="R64" t="n">
-        <v>6836796</v>
+        <v>6836813</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7164,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727544</v>
+        <v>118727583</v>
       </c>
       <c r="B65" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,35 +7180,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456065</v>
+        <v>456050</v>
       </c>
       <c r="R65" t="n">
-        <v>6836867</v>
+        <v>6836858</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7239,10 +7266,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118727530</v>
+        <v>118727598</v>
       </c>
       <c r="B66" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7255,35 +7282,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455892</v>
+        <v>455878</v>
       </c>
       <c r="R66" t="n">
-        <v>6836753</v>
+        <v>6836925</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7342,10 +7368,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118727623</v>
+        <v>118727517</v>
       </c>
       <c r="B67" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7358,34 +7384,35 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455802</v>
+        <v>455986</v>
       </c>
       <c r="R67" t="n">
-        <v>6837089</v>
+        <v>6836980</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7444,10 +7471,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118727594</v>
+        <v>118727527</v>
       </c>
       <c r="B68" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7460,34 +7487,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456008</v>
+        <v>455903</v>
       </c>
       <c r="R68" t="n">
-        <v>6836969</v>
+        <v>6836778</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7546,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727624</v>
+        <v>118727539</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7562,34 +7590,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455844</v>
+        <v>456035</v>
       </c>
       <c r="R69" t="n">
-        <v>6837118</v>
+        <v>6836794</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7648,7 +7677,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727631</v>
+        <v>118727635</v>
       </c>
       <c r="B70" t="n">
         <v>78484</v>
@@ -7688,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455914</v>
+        <v>455915</v>
       </c>
       <c r="R70" t="n">
-        <v>6836965</v>
+        <v>6836927</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7750,10 +7779,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727549</v>
+        <v>118727636</v>
       </c>
       <c r="B71" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7766,35 +7795,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455956</v>
+        <v>455925</v>
       </c>
       <c r="R71" t="n">
-        <v>6836745</v>
+        <v>6836919</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7853,10 +7881,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727545</v>
+        <v>118727585</v>
       </c>
       <c r="B72" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7869,35 +7897,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455700</v>
+        <v>455930</v>
       </c>
       <c r="R72" t="n">
-        <v>6837083</v>
+        <v>6836897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7956,10 +7983,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727612</v>
+        <v>118727550</v>
       </c>
       <c r="B73" t="n">
-        <v>90654</v>
+        <v>79073</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7968,38 +7995,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455930</v>
+        <v>455970</v>
       </c>
       <c r="R73" t="n">
-        <v>6836843</v>
+        <v>6836763</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8058,10 +8086,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118727508</v>
+        <v>118727618</v>
       </c>
       <c r="B74" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8074,35 +8102,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455765</v>
+        <v>455724</v>
       </c>
       <c r="R74" t="n">
-        <v>6837108</v>
+        <v>6837080</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8161,10 +8188,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118727596</v>
+        <v>118727637</v>
       </c>
       <c r="B75" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8177,21 +8204,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8201,10 +8228,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455956</v>
+        <v>455922</v>
       </c>
       <c r="R75" t="n">
-        <v>6837009</v>
+        <v>6836913</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,10 +8290,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118727586</v>
+        <v>118727507</v>
       </c>
       <c r="B76" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8279,34 +8306,35 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455865</v>
+        <v>455726</v>
       </c>
       <c r="R76" t="n">
-        <v>6836943</v>
+        <v>6837099</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,10 +8393,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118727665</v>
+        <v>118727503</v>
       </c>
       <c r="B77" t="n">
-        <v>77868</v>
+        <v>78518</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8381,21 +8409,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8405,10 +8433,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>455701</v>
+        <v>456028</v>
       </c>
       <c r="R77" t="n">
-        <v>6837084</v>
+        <v>6836799</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,10 +8495,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118727630</v>
+        <v>118727597</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8483,21 +8511,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8507,10 +8535,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455860</v>
+        <v>455943</v>
       </c>
       <c r="R78" t="n">
-        <v>6837129</v>
+        <v>6836998</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8569,10 +8597,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118727618</v>
+        <v>118727594</v>
       </c>
       <c r="B79" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8585,21 +8613,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8609,10 +8637,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455724</v>
+        <v>456008</v>
       </c>
       <c r="R79" t="n">
-        <v>6837080</v>
+        <v>6836969</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8671,10 +8699,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118727513</v>
+        <v>118727554</v>
       </c>
       <c r="B80" t="n">
-        <v>78518</v>
+        <v>79073</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8687,21 +8715,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8712,10 +8740,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455971</v>
+        <v>456036</v>
       </c>
       <c r="R80" t="n">
-        <v>6836747</v>
+        <v>6836795</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8774,10 +8802,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118727608</v>
+        <v>118727502</v>
       </c>
       <c r="B81" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8790,21 +8818,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8814,10 +8842,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456041</v>
+        <v>456023</v>
       </c>
       <c r="R81" t="n">
-        <v>6836795</v>
+        <v>6836783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8876,10 +8904,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118727541</v>
+        <v>118727624</v>
       </c>
       <c r="B82" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8892,35 +8920,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>456048</v>
+        <v>455844</v>
       </c>
       <c r="R82" t="n">
-        <v>6836813</v>
+        <v>6837118</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8979,10 +9006,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118727525</v>
+        <v>118727667</v>
       </c>
       <c r="B83" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8995,35 +9022,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>455924</v>
+        <v>456035</v>
       </c>
       <c r="R83" t="n">
-        <v>6836801</v>
+        <v>6836796</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9082,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118727547</v>
+        <v>118727593</v>
       </c>
       <c r="B84" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9098,35 +9124,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>455904</v>
+        <v>456027</v>
       </c>
       <c r="R84" t="n">
-        <v>6836778</v>
+        <v>6836806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9185,7 +9210,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118727561</v>
+        <v>118727562</v>
       </c>
       <c r="B85" t="n">
         <v>78583</v>
@@ -9225,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>455930</v>
+        <v>455956</v>
       </c>
       <c r="R85" t="n">
-        <v>6836890</v>
+        <v>6836833</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9287,10 +9312,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118727632</v>
+        <v>118727611</v>
       </c>
       <c r="B86" t="n">
-        <v>78484</v>
+        <v>90654</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9299,25 +9324,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9327,10 +9352,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>455916</v>
+        <v>455716</v>
       </c>
       <c r="R86" t="n">
-        <v>6836963</v>
+        <v>6837046</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9389,10 +9414,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727506</v>
+        <v>118727523</v>
       </c>
       <c r="B87" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9405,21 +9430,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9430,10 +9455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>455726</v>
+        <v>455933</v>
       </c>
       <c r="R87" t="n">
-        <v>6837083</v>
+        <v>6836859</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9492,10 +9517,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727609</v>
+        <v>118727664</v>
       </c>
       <c r="B88" t="n">
-        <v>78220</v>
+        <v>77416</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9508,21 +9533,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9532,10 +9557,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456053</v>
+        <v>456028</v>
       </c>
       <c r="R88" t="n">
-        <v>6836858</v>
+        <v>6836814</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9594,10 +9619,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118727531</v>
+        <v>118727639</v>
       </c>
       <c r="B89" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9610,35 +9635,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455918</v>
+        <v>455967</v>
       </c>
       <c r="R89" t="n">
-        <v>6836750</v>
+        <v>6836746</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9697,10 +9721,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118727543</v>
+        <v>118727627</v>
       </c>
       <c r="B90" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9713,35 +9737,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456050</v>
+        <v>455891</v>
       </c>
       <c r="R90" t="n">
-        <v>6836858</v>
+        <v>6836950</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9800,10 +9823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118727598</v>
+        <v>118727660</v>
       </c>
       <c r="B91" t="n">
-        <v>78221</v>
+        <v>78129</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9816,21 +9839,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9840,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>455878</v>
+        <v>456065</v>
       </c>
       <c r="R91" t="n">
-        <v>6836925</v>
+        <v>6836867</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9902,10 +9925,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118727601</v>
+        <v>118727519</v>
       </c>
       <c r="B92" t="n">
-        <v>80441</v>
+        <v>79102</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9918,34 +9941,35 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>455913</v>
+        <v>455850</v>
       </c>
       <c r="R92" t="n">
-        <v>6836820</v>
+        <v>6837094</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10004,7 +10028,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118727606</v>
+        <v>118727607</v>
       </c>
       <c r="B93" t="n">
         <v>78220</v>
@@ -10044,10 +10068,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456025</v>
+        <v>456027</v>
       </c>
       <c r="R93" t="n">
-        <v>6836801</v>
+        <v>6836806</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10208,10 +10232,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118727595</v>
+        <v>118727553</v>
       </c>
       <c r="B95" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10224,34 +10248,35 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455986</v>
+        <v>456026</v>
       </c>
       <c r="R95" t="n">
-        <v>6836980</v>
+        <v>6836798</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10310,10 +10335,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118727560</v>
+        <v>118727508</v>
       </c>
       <c r="B96" t="n">
-        <v>78583</v>
+        <v>78518</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10326,45 +10351,35 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455904</v>
+        <v>455765</v>
       </c>
       <c r="R96" t="n">
-        <v>6836777</v>
+        <v>6837108</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10405,7 +10420,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10424,10 +10438,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118727638</v>
+        <v>118727532</v>
       </c>
       <c r="B97" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10440,34 +10454,35 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455933</v>
+        <v>455926</v>
       </c>
       <c r="R97" t="n">
-        <v>6836917</v>
+        <v>6836752</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10526,10 +10541,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118727529</v>
+        <v>118727604</v>
       </c>
       <c r="B98" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10542,35 +10557,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455885</v>
+        <v>455931</v>
       </c>
       <c r="R98" t="n">
-        <v>6836757</v>
+        <v>6836858</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,10 +10643,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118727662</v>
+        <v>118727595</v>
       </c>
       <c r="B99" t="n">
-        <v>77416</v>
+        <v>78221</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10645,21 +10659,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10669,10 +10683,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455700</v>
+        <v>455986</v>
       </c>
       <c r="R99" t="n">
-        <v>6837084</v>
+        <v>6836980</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10731,10 +10745,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118727584</v>
+        <v>118727546</v>
       </c>
       <c r="B100" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10747,31 +10761,32 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456053</v>
+        <v>455932</v>
       </c>
       <c r="R100" t="n">
         <v>6836858</v>
@@ -10833,7 +10848,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118727620</v>
+        <v>118727631</v>
       </c>
       <c r="B101" t="n">
         <v>78484</v>
@@ -10873,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455733</v>
+        <v>455914</v>
       </c>
       <c r="R101" t="n">
-        <v>6837103</v>
+        <v>6836965</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10935,10 +10950,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118727629</v>
+        <v>118727610</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10951,21 +10966,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10975,10 +10990,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455870</v>
+        <v>455955</v>
       </c>
       <c r="R102" t="n">
-        <v>6837153</v>
+        <v>6837009</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11037,10 +11052,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118727502</v>
+        <v>118727606</v>
       </c>
       <c r="B103" t="n">
-        <v>78518</v>
+        <v>78220</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11053,21 +11068,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11077,10 +11092,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456023</v>
+        <v>456025</v>
       </c>
       <c r="R103" t="n">
-        <v>6836783</v>
+        <v>6836801</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11139,7 +11154,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118727655</v>
+        <v>118727658</v>
       </c>
       <c r="B104" t="n">
         <v>78129</v>
@@ -11179,10 +11194,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>455973</v>
+        <v>455957</v>
       </c>
       <c r="R104" t="n">
-        <v>6836775</v>
+        <v>6836744</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11241,10 +11256,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118727527</v>
+        <v>118727640</v>
       </c>
       <c r="B105" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11257,35 +11272,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455903</v>
+        <v>455987</v>
       </c>
       <c r="R105" t="n">
-        <v>6836778</v>
+        <v>6836765</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11344,7 +11358,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118727592</v>
+        <v>118727586</v>
       </c>
       <c r="B106" t="n">
         <v>78221</v>
@@ -11384,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>456025</v>
+        <v>455865</v>
       </c>
       <c r="R106" t="n">
-        <v>6836800</v>
+        <v>6836943</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11446,10 +11460,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118727597</v>
+        <v>118727560</v>
       </c>
       <c r="B107" t="n">
-        <v>78221</v>
+        <v>78583</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11462,34 +11476,45 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455943</v>
+        <v>455904</v>
       </c>
       <c r="R107" t="n">
-        <v>6836998</v>
+        <v>6836777</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11530,6 +11555,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11548,10 +11574,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118727550</v>
+        <v>118727521</v>
       </c>
       <c r="B108" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11564,21 +11590,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11589,10 +11615,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>455970</v>
+        <v>455919</v>
       </c>
       <c r="R108" t="n">
-        <v>6836763</v>
+        <v>6836937</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11651,7 +11677,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118727521</v>
+        <v>118727530</v>
       </c>
       <c r="B109" t="n">
         <v>79102</v>
@@ -11692,10 +11718,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>455919</v>
+        <v>455892</v>
       </c>
       <c r="R109" t="n">
-        <v>6836937</v>
+        <v>6836753</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11754,10 +11780,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727558</v>
+        <v>118727590</v>
       </c>
       <c r="B110" t="n">
-        <v>78583</v>
+        <v>78221</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11770,45 +11796,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456036</v>
+        <v>455955</v>
       </c>
       <c r="R110" t="n">
-        <v>6836794</v>
+        <v>6836833</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11849,7 +11864,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11868,10 +11882,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727599</v>
+        <v>118727510</v>
       </c>
       <c r="B111" t="n">
-        <v>90966</v>
+        <v>78518</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11884,34 +11898,35 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5467</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455957</v>
+        <v>455912</v>
       </c>
       <c r="R111" t="n">
-        <v>6836745</v>
+        <v>6836969</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11985,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727582</v>
+        <v>118727600</v>
       </c>
       <c r="B112" t="n">
-        <v>57290</v>
+        <v>80441</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11986,42 +12001,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455915</v>
+        <v>455702</v>
       </c>
       <c r="R112" t="n">
-        <v>6836954</v>
+        <v>6837084</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12054,11 +12061,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,10 +12087,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727660</v>
+        <v>118727557</v>
       </c>
       <c r="B113" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12101,34 +12103,35 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456065</v>
+        <v>456053</v>
       </c>
       <c r="R113" t="n">
-        <v>6836867</v>
+        <v>6836858</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12187,10 +12190,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727607</v>
+        <v>118727542</v>
       </c>
       <c r="B114" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12203,34 +12206,35 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456027</v>
+        <v>456022</v>
       </c>
       <c r="R114" t="n">
-        <v>6836806</v>
+        <v>6836819</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12289,10 +12293,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727585</v>
+        <v>118727524</v>
       </c>
       <c r="B115" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12305,34 +12309,35 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455930</v>
+        <v>455955</v>
       </c>
       <c r="R115" t="n">
-        <v>6836897</v>
+        <v>6836833</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12391,10 +12396,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727633</v>
+        <v>118727548</v>
       </c>
       <c r="B116" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12407,34 +12412,35 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455917</v>
+        <v>455926</v>
       </c>
       <c r="R116" t="n">
-        <v>6836957</v>
+        <v>6836752</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12493,10 +12499,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727557</v>
+        <v>118727584</v>
       </c>
       <c r="B117" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12509,25 +12515,24 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
@@ -12596,10 +12601,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727548</v>
+        <v>118727629</v>
       </c>
       <c r="B118" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12612,35 +12617,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455926</v>
+        <v>455870</v>
       </c>
       <c r="R118" t="n">
-        <v>6836752</v>
+        <v>6837153</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12699,10 +12703,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727542</v>
+        <v>118727622</v>
       </c>
       <c r="B119" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12715,35 +12719,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>456022</v>
+        <v>455747</v>
       </c>
       <c r="R119" t="n">
-        <v>6836819</v>
+        <v>6837101</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12802,10 +12805,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727518</v>
+        <v>118727623</v>
       </c>
       <c r="B120" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12818,35 +12821,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455952</v>
+        <v>455802</v>
       </c>
       <c r="R120" t="n">
-        <v>6836992</v>
+        <v>6837089</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12905,10 +12907,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118727546</v>
+        <v>118727668</v>
       </c>
       <c r="B121" t="n">
-        <v>79073</v>
+        <v>77868</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12921,35 +12923,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455932</v>
+        <v>456028</v>
       </c>
       <c r="R121" t="n">
-        <v>6836858</v>
+        <v>6836814</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13008,7 +13009,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118727587</v>
+        <v>118727591</v>
       </c>
       <c r="B122" t="n">
         <v>78221</v>
@@ -13048,10 +13049,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455933</v>
+        <v>455924</v>
       </c>
       <c r="R122" t="n">
-        <v>6836859</v>
+        <v>6836800</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13110,10 +13111,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118727626</v>
+        <v>118727651</v>
       </c>
       <c r="B123" t="n">
-        <v>78484</v>
+        <v>90749</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13122,25 +13123,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13150,10 +13151,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>455897</v>
+        <v>455972</v>
       </c>
       <c r="R123" t="n">
-        <v>6836935</v>
+        <v>6836775</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13212,10 +13213,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118727510</v>
+        <v>118727630</v>
       </c>
       <c r="B124" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,35 +13229,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>455912</v>
+        <v>455860</v>
       </c>
       <c r="R124" t="n">
-        <v>6836969</v>
+        <v>6837129</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13315,7 +13315,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118727526</v>
+        <v>118727543</v>
       </c>
       <c r="B125" t="n">
         <v>79102</v>
@@ -13356,10 +13356,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>455943</v>
+        <v>456050</v>
       </c>
       <c r="R125" t="n">
-        <v>6836795</v>
+        <v>6836858</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13418,10 +13418,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118727604</v>
+        <v>118727579</v>
       </c>
       <c r="B126" t="n">
-        <v>78220</v>
+        <v>78573</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13430,25 +13430,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6450</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13458,10 +13458,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455931</v>
+        <v>455885</v>
       </c>
       <c r="R126" t="n">
-        <v>6836858</v>
+        <v>6836936</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13520,10 +13520,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118727537</v>
+        <v>118727601</v>
       </c>
       <c r="B127" t="n">
-        <v>79102</v>
+        <v>80441</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13536,35 +13536,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>456027</v>
+        <v>455913</v>
       </c>
       <c r="R127" t="n">
-        <v>6836806</v>
+        <v>6836820</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13623,7 +13622,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118727524</v>
+        <v>118727525</v>
       </c>
       <c r="B128" t="n">
         <v>79102</v>
@@ -13664,10 +13663,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>455955</v>
+        <v>455924</v>
       </c>
       <c r="R128" t="n">
-        <v>6836833</v>
+        <v>6836801</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13726,10 +13725,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118727611</v>
+        <v>118727599</v>
       </c>
       <c r="B129" t="n">
-        <v>90654</v>
+        <v>90966</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13738,25 +13737,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1503</v>
+        <v>5467</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13765,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>455716</v>
+        <v>455957</v>
       </c>
       <c r="R129" t="n">
-        <v>6837046</v>
+        <v>6836745</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13828,10 +13827,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118727652</v>
+        <v>118727596</v>
       </c>
       <c r="B130" t="n">
-        <v>94513</v>
+        <v>78221</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13840,25 +13839,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2170</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13867,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455841</v>
+        <v>455956</v>
       </c>
       <c r="R130" t="n">
-        <v>6837101</v>
+        <v>6837009</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13930,10 +13929,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118727658</v>
+        <v>118727592</v>
       </c>
       <c r="B131" t="n">
-        <v>78129</v>
+        <v>78221</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13946,21 +13945,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13969,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455957</v>
+        <v>456025</v>
       </c>
       <c r="R131" t="n">
-        <v>6836744</v>
+        <v>6836800</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14032,7 +14031,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118727593</v>
+        <v>118727588</v>
       </c>
       <c r="B132" t="n">
         <v>78221</v>
@@ -14072,10 +14071,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>456027</v>
+        <v>455938</v>
       </c>
       <c r="R132" t="n">
-        <v>6836806</v>
+        <v>6836861</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14134,10 +14133,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118727603</v>
+        <v>118727513</v>
       </c>
       <c r="B133" t="n">
-        <v>80441</v>
+        <v>78518</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14150,34 +14149,35 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456024</v>
+        <v>455971</v>
       </c>
       <c r="R133" t="n">
-        <v>6836818</v>
+        <v>6836747</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14236,10 +14236,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118727503</v>
+        <v>118727561</v>
       </c>
       <c r="B134" t="n">
-        <v>78518</v>
+        <v>78583</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,21 +14252,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14276,10 +14276,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456028</v>
+        <v>455930</v>
       </c>
       <c r="R134" t="n">
-        <v>6836799</v>
+        <v>6836890</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14338,10 +14338,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118727635</v>
+        <v>118727518</v>
       </c>
       <c r="B135" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14354,34 +14354,35 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455915</v>
+        <v>455952</v>
       </c>
       <c r="R135" t="n">
-        <v>6836927</v>
+        <v>6836992</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14440,7 +14441,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118727519</v>
+        <v>118727544</v>
       </c>
       <c r="B136" t="n">
         <v>79102</v>
@@ -14481,10 +14482,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455850</v>
+        <v>456065</v>
       </c>
       <c r="R136" t="n">
-        <v>6837094</v>
+        <v>6836867</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14543,7 +14544,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118727532</v>
+        <v>118727533</v>
       </c>
       <c r="B137" t="n">
         <v>79102</v>
@@ -14584,10 +14585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455926</v>
+        <v>455956</v>
       </c>
       <c r="R137" t="n">
-        <v>6836752</v>
+        <v>6836745</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14646,10 +14647,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118727591</v>
+        <v>118727662</v>
       </c>
       <c r="B138" t="n">
-        <v>78221</v>
+        <v>77416</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14662,21 +14663,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14686,10 +14687,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455924</v>
+        <v>455700</v>
       </c>
       <c r="R138" t="n">
-        <v>6836800</v>
+        <v>6837084</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14748,10 +14749,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118727583</v>
+        <v>118727632</v>
       </c>
       <c r="B139" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14764,21 +14765,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14788,10 +14789,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456050</v>
+        <v>455916</v>
       </c>
       <c r="R139" t="n">
-        <v>6836858</v>
+        <v>6836963</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14850,10 +14851,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118727507</v>
+        <v>118727626</v>
       </c>
       <c r="B140" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14866,35 +14867,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455726</v>
+        <v>455897</v>
       </c>
       <c r="R140" t="n">
-        <v>6837099</v>
+        <v>6836935</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14953,10 +14953,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118727539</v>
+        <v>118727652</v>
       </c>
       <c r="B141" t="n">
-        <v>79102</v>
+        <v>94513</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14965,39 +14965,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>456035</v>
+        <v>455841</v>
       </c>
       <c r="R141" t="n">
-        <v>6836794</v>
+        <v>6837101</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15056,10 +15055,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118727588</v>
+        <v>118727526</v>
       </c>
       <c r="B142" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15072,34 +15071,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455938</v>
+        <v>455943</v>
       </c>
       <c r="R142" t="n">
-        <v>6836861</v>
+        <v>6836795</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15158,10 +15158,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118727554</v>
+        <v>118727531</v>
       </c>
       <c r="B143" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15174,21 +15174,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>456036</v>
+        <v>455918</v>
       </c>
       <c r="R143" t="n">
-        <v>6836795</v>
+        <v>6836750</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614103</v>
+        <v>118614110</v>
       </c>
       <c r="B6" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455886</v>
+        <v>456021</v>
       </c>
       <c r="R6" t="n">
-        <v>6836900</v>
+        <v>6836968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614110</v>
+        <v>118614103</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456021</v>
+        <v>455886</v>
       </c>
       <c r="R7" t="n">
-        <v>6836968</v>
+        <v>6836900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118614088</v>
+        <v>118614095</v>
       </c>
       <c r="B29" t="n">
-        <v>57443</v>
+        <v>78220</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455935</v>
+        <v>455985</v>
       </c>
       <c r="R29" t="n">
-        <v>6836858</v>
+        <v>6836979</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118614095</v>
+        <v>118614108</v>
       </c>
       <c r="B30" t="n">
         <v>78220</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455985</v>
+        <v>455960</v>
       </c>
       <c r="R30" t="n">
-        <v>6836979</v>
+        <v>6837047</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,7 +3646,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118614108</v>
+        <v>118614100</v>
       </c>
       <c r="B31" t="n">
         <v>78220</v>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455960</v>
+        <v>455939</v>
       </c>
       <c r="R31" t="n">
-        <v>6837047</v>
+        <v>6836859</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118614100</v>
+        <v>118614088</v>
       </c>
       <c r="B32" t="n">
-        <v>78220</v>
+        <v>57443</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455939</v>
+        <v>455935</v>
       </c>
       <c r="R32" t="n">
-        <v>6836859</v>
+        <v>6836858</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118614091</v>
+        <v>118614106</v>
       </c>
       <c r="B33" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455881</v>
+        <v>455886</v>
       </c>
       <c r="R33" t="n">
-        <v>6836923</v>
+        <v>6836975</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118614106</v>
+        <v>118614091</v>
       </c>
       <c r="B34" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455886</v>
+        <v>455881</v>
       </c>
       <c r="R34" t="n">
-        <v>6836975</v>
+        <v>6836923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118727609</v>
+        <v>118727506</v>
       </c>
       <c r="B39" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4503,34 +4503,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456053</v>
+        <v>455726</v>
       </c>
       <c r="R39" t="n">
-        <v>6836858</v>
+        <v>6837083</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4589,10 +4590,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727612</v>
+        <v>118727655</v>
       </c>
       <c r="B40" t="n">
-        <v>90654</v>
+        <v>78129</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4601,25 +4602,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4630,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455930</v>
+        <v>455973</v>
       </c>
       <c r="R40" t="n">
-        <v>6836843</v>
+        <v>6836775</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727625</v>
+        <v>118727612</v>
       </c>
       <c r="B41" t="n">
-        <v>78484</v>
+        <v>90654</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4703,25 +4704,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455868</v>
+        <v>455930</v>
       </c>
       <c r="R41" t="n">
-        <v>6837146</v>
+        <v>6836843</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4793,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727529</v>
+        <v>118727648</v>
       </c>
       <c r="B42" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4809,35 +4810,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455885</v>
+        <v>456055</v>
       </c>
       <c r="R42" t="n">
-        <v>6836757</v>
+        <v>6836875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727520</v>
+        <v>118727529</v>
       </c>
       <c r="B43" t="n">
         <v>79102</v>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455867</v>
+        <v>455885</v>
       </c>
       <c r="R43" t="n">
-        <v>6836942</v>
+        <v>6836757</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727537</v>
+        <v>118727520</v>
       </c>
       <c r="B44" t="n">
         <v>79102</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456027</v>
+        <v>455867</v>
       </c>
       <c r="R44" t="n">
-        <v>6836806</v>
+        <v>6836942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727506</v>
+        <v>118727537</v>
       </c>
       <c r="B45" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455726</v>
+        <v>456027</v>
       </c>
       <c r="R45" t="n">
-        <v>6837083</v>
+        <v>6836806</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727655</v>
+        <v>118727625</v>
       </c>
       <c r="B46" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5221,21 +5221,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455973</v>
+        <v>455868</v>
       </c>
       <c r="R46" t="n">
-        <v>6836775</v>
+        <v>6837146</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,10 +5307,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727648</v>
+        <v>118727609</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5323,21 +5323,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456055</v>
+        <v>456053</v>
       </c>
       <c r="R47" t="n">
-        <v>6836875</v>
+        <v>6836858</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727583</v>
+        <v>118727517</v>
       </c>
       <c r="B65" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7180,34 +7180,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456050</v>
+        <v>455986</v>
       </c>
       <c r="R65" t="n">
-        <v>6836858</v>
+        <v>6836980</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7266,10 +7267,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118727598</v>
+        <v>118727527</v>
       </c>
       <c r="B66" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7282,34 +7283,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455878</v>
+        <v>455903</v>
       </c>
       <c r="R66" t="n">
-        <v>6836925</v>
+        <v>6836778</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7368,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118727517</v>
+        <v>118727583</v>
       </c>
       <c r="B67" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7384,35 +7386,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455986</v>
+        <v>456050</v>
       </c>
       <c r="R67" t="n">
-        <v>6836980</v>
+        <v>6836858</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7471,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118727527</v>
+        <v>118727598</v>
       </c>
       <c r="B68" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7487,35 +7488,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455903</v>
+        <v>455878</v>
       </c>
       <c r="R68" t="n">
-        <v>6836778</v>
+        <v>6836925</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727539</v>
+        <v>118727550</v>
       </c>
       <c r="B69" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7590,21 +7590,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456035</v>
+        <v>455970</v>
       </c>
       <c r="R69" t="n">
-        <v>6836794</v>
+        <v>6836763</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727635</v>
+        <v>118727585</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,21 +7693,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455915</v>
+        <v>455930</v>
       </c>
       <c r="R70" t="n">
-        <v>6836927</v>
+        <v>6836897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727636</v>
+        <v>118727539</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7795,34 +7795,35 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455925</v>
+        <v>456035</v>
       </c>
       <c r="R71" t="n">
-        <v>6836919</v>
+        <v>6836794</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7881,10 +7882,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727585</v>
+        <v>118727635</v>
       </c>
       <c r="B72" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7897,21 +7898,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7922,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455930</v>
+        <v>455915</v>
       </c>
       <c r="R72" t="n">
-        <v>6836897</v>
+        <v>6836927</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7983,10 +7984,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727550</v>
+        <v>118727636</v>
       </c>
       <c r="B73" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7999,35 +8000,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455970</v>
+        <v>455925</v>
       </c>
       <c r="R73" t="n">
-        <v>6836763</v>
+        <v>6836919</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118727593</v>
+        <v>118727562</v>
       </c>
       <c r="B84" t="n">
-        <v>78221</v>
+        <v>78583</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456027</v>
+        <v>455956</v>
       </c>
       <c r="R84" t="n">
-        <v>6836806</v>
+        <v>6836833</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118727562</v>
+        <v>118727611</v>
       </c>
       <c r="B85" t="n">
-        <v>78583</v>
+        <v>90654</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9222,25 +9222,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>967</v>
+        <v>1503</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>455956</v>
+        <v>455716</v>
       </c>
       <c r="R85" t="n">
-        <v>6836833</v>
+        <v>6837046</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118727611</v>
+        <v>118727664</v>
       </c>
       <c r="B86" t="n">
-        <v>90654</v>
+        <v>77416</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9324,25 +9324,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>455716</v>
+        <v>456028</v>
       </c>
       <c r="R86" t="n">
-        <v>6837046</v>
+        <v>6836814</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727523</v>
+        <v>118727593</v>
       </c>
       <c r="B87" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,35 +9430,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>455933</v>
+        <v>456027</v>
       </c>
       <c r="R87" t="n">
-        <v>6836859</v>
+        <v>6836806</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9517,10 +9516,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727664</v>
+        <v>118727523</v>
       </c>
       <c r="B88" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,34 +9532,35 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>456028</v>
+        <v>455933</v>
       </c>
       <c r="R88" t="n">
-        <v>6836814</v>
+        <v>6836859</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10848,7 +10848,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118727631</v>
+        <v>118727640</v>
       </c>
       <c r="B101" t="n">
         <v>78484</v>
@@ -10888,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455914</v>
+        <v>455987</v>
       </c>
       <c r="R101" t="n">
-        <v>6836965</v>
+        <v>6836765</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11154,10 +11154,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118727658</v>
+        <v>118727631</v>
       </c>
       <c r="B104" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11170,21 +11170,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>455957</v>
+        <v>455914</v>
       </c>
       <c r="R104" t="n">
-        <v>6836744</v>
+        <v>6836965</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11256,10 +11256,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118727640</v>
+        <v>118727658</v>
       </c>
       <c r="B105" t="n">
-        <v>78484</v>
+        <v>78129</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455987</v>
+        <v>455957</v>
       </c>
       <c r="R105" t="n">
-        <v>6836765</v>
+        <v>6836744</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11780,10 +11780,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727590</v>
+        <v>118727510</v>
       </c>
       <c r="B110" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11796,34 +11796,35 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>455955</v>
+        <v>455912</v>
       </c>
       <c r="R110" t="n">
-        <v>6836833</v>
+        <v>6836969</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11882,10 +11883,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727510</v>
+        <v>118727600</v>
       </c>
       <c r="B111" t="n">
-        <v>78518</v>
+        <v>80441</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11898,35 +11899,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455912</v>
+        <v>455702</v>
       </c>
       <c r="R111" t="n">
-        <v>6836969</v>
+        <v>6837084</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11985,10 +11985,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727600</v>
+        <v>118727557</v>
       </c>
       <c r="B112" t="n">
-        <v>80441</v>
+        <v>79073</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12001,34 +12001,35 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455702</v>
+        <v>456053</v>
       </c>
       <c r="R112" t="n">
-        <v>6837084</v>
+        <v>6836858</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12087,10 +12088,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727557</v>
+        <v>118727590</v>
       </c>
       <c r="B113" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12103,35 +12104,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456053</v>
+        <v>455955</v>
       </c>
       <c r="R113" t="n">
-        <v>6836858</v>
+        <v>6836833</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727542</v>
+        <v>118727668</v>
       </c>
       <c r="B114" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12206,35 +12206,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456022</v>
+        <v>456028</v>
       </c>
       <c r="R114" t="n">
-        <v>6836819</v>
+        <v>6836814</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12293,7 +12292,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727524</v>
+        <v>118727542</v>
       </c>
       <c r="B115" t="n">
         <v>79102</v>
@@ -12334,10 +12333,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455955</v>
+        <v>456022</v>
       </c>
       <c r="R115" t="n">
-        <v>6836833</v>
+        <v>6836819</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12396,10 +12395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727548</v>
+        <v>118727524</v>
       </c>
       <c r="B116" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12412,21 +12411,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12437,10 +12436,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455926</v>
+        <v>455955</v>
       </c>
       <c r="R116" t="n">
-        <v>6836752</v>
+        <v>6836833</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12499,10 +12498,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727584</v>
+        <v>118727629</v>
       </c>
       <c r="B117" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12515,21 +12514,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12539,10 +12538,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456053</v>
+        <v>455870</v>
       </c>
       <c r="R117" t="n">
-        <v>6836858</v>
+        <v>6837153</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12601,7 +12600,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727629</v>
+        <v>118727622</v>
       </c>
       <c r="B118" t="n">
         <v>78484</v>
@@ -12641,10 +12640,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455870</v>
+        <v>455747</v>
       </c>
       <c r="R118" t="n">
-        <v>6837153</v>
+        <v>6837101</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12703,7 +12702,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727622</v>
+        <v>118727623</v>
       </c>
       <c r="B119" t="n">
         <v>78484</v>
@@ -12743,10 +12742,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455747</v>
+        <v>455802</v>
       </c>
       <c r="R119" t="n">
-        <v>6837101</v>
+        <v>6837089</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12805,10 +12804,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727623</v>
+        <v>118727548</v>
       </c>
       <c r="B120" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12821,34 +12820,35 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455802</v>
+        <v>455926</v>
       </c>
       <c r="R120" t="n">
-        <v>6837089</v>
+        <v>6836752</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12907,10 +12907,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118727668</v>
+        <v>118727584</v>
       </c>
       <c r="B121" t="n">
-        <v>77868</v>
+        <v>78221</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12923,21 +12923,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12947,10 +12947,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>456028</v>
+        <v>456053</v>
       </c>
       <c r="R121" t="n">
-        <v>6836814</v>
+        <v>6836858</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13315,10 +13315,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118727543</v>
+        <v>118727601</v>
       </c>
       <c r="B125" t="n">
-        <v>79102</v>
+        <v>80441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13331,35 +13331,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>456050</v>
+        <v>455913</v>
       </c>
       <c r="R125" t="n">
-        <v>6836858</v>
+        <v>6836820</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13418,10 +13417,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118727579</v>
+        <v>118727543</v>
       </c>
       <c r="B126" t="n">
-        <v>78573</v>
+        <v>79102</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13430,38 +13429,39 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455885</v>
+        <v>456050</v>
       </c>
       <c r="R126" t="n">
-        <v>6836936</v>
+        <v>6836858</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13520,10 +13520,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118727601</v>
+        <v>118727579</v>
       </c>
       <c r="B127" t="n">
-        <v>80441</v>
+        <v>78573</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13532,25 +13532,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1049</v>
+        <v>6450</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13560,10 +13560,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455913</v>
+        <v>455885</v>
       </c>
       <c r="R127" t="n">
-        <v>6836820</v>
+        <v>6836936</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13929,10 +13929,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118727592</v>
+        <v>118727561</v>
       </c>
       <c r="B131" t="n">
-        <v>78221</v>
+        <v>78583</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13945,21 +13945,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13969,10 +13969,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>456025</v>
+        <v>455930</v>
       </c>
       <c r="R131" t="n">
-        <v>6836800</v>
+        <v>6836890</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14031,10 +14031,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118727588</v>
+        <v>118727518</v>
       </c>
       <c r="B132" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14047,34 +14047,35 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455938</v>
+        <v>455952</v>
       </c>
       <c r="R132" t="n">
-        <v>6836861</v>
+        <v>6836992</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14133,10 +14134,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118727513</v>
+        <v>118727544</v>
       </c>
       <c r="B133" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14149,21 +14150,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14174,10 +14175,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455971</v>
+        <v>456065</v>
       </c>
       <c r="R133" t="n">
-        <v>6836747</v>
+        <v>6836867</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14236,10 +14237,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118727561</v>
+        <v>118727533</v>
       </c>
       <c r="B134" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,34 +14253,35 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455930</v>
+        <v>455956</v>
       </c>
       <c r="R134" t="n">
-        <v>6836890</v>
+        <v>6836745</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14338,10 +14340,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118727518</v>
+        <v>118727662</v>
       </c>
       <c r="B135" t="n">
-        <v>79102</v>
+        <v>77416</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14354,35 +14356,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455952</v>
+        <v>455700</v>
       </c>
       <c r="R135" t="n">
-        <v>6836992</v>
+        <v>6837084</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14441,10 +14442,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118727544</v>
+        <v>118727513</v>
       </c>
       <c r="B136" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,21 +14458,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14482,10 +14483,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>456065</v>
+        <v>455971</v>
       </c>
       <c r="R136" t="n">
-        <v>6836867</v>
+        <v>6836747</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14544,10 +14545,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118727533</v>
+        <v>118727592</v>
       </c>
       <c r="B137" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14560,35 +14561,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455956</v>
+        <v>456025</v>
       </c>
       <c r="R137" t="n">
-        <v>6836745</v>
+        <v>6836800</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14647,10 +14647,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118727662</v>
+        <v>118727588</v>
       </c>
       <c r="B138" t="n">
-        <v>77416</v>
+        <v>78221</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14663,21 +14663,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455700</v>
+        <v>455938</v>
       </c>
       <c r="R138" t="n">
-        <v>6837084</v>
+        <v>6836861</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118614079</v>
+        <v>118614099</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455886</v>
+        <v>455969</v>
       </c>
       <c r="R2" t="n">
-        <v>6836900</v>
+        <v>6836868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118614081</v>
+        <v>118614084</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455942</v>
+        <v>456032</v>
       </c>
       <c r="R3" t="n">
-        <v>6837031</v>
+        <v>6836895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118614111</v>
+        <v>118614096</v>
       </c>
       <c r="B4" t="n">
-        <v>78129</v>
+        <v>78220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455971</v>
+        <v>456010</v>
       </c>
       <c r="R4" t="n">
-        <v>6837047</v>
+        <v>6836965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118614087</v>
+        <v>118614092</v>
       </c>
       <c r="B5" t="n">
-        <v>78583</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455959</v>
+        <v>455960</v>
       </c>
       <c r="R5" t="n">
-        <v>6837052</v>
+        <v>6837047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614110</v>
+        <v>118614088</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456021</v>
+        <v>455935</v>
       </c>
       <c r="R6" t="n">
-        <v>6836968</v>
+        <v>6836858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614103</v>
+        <v>118614111</v>
       </c>
       <c r="B7" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455886</v>
+        <v>455971</v>
       </c>
       <c r="R7" t="n">
-        <v>6836900</v>
+        <v>6837047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118614089</v>
+        <v>118614095</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>78220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,42 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456021</v>
+        <v>455985</v>
       </c>
       <c r="R8" t="n">
-        <v>6837003</v>
+        <v>6836979</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118614093</v>
+        <v>118614076</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
+        <v>78518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456008</v>
+        <v>456018</v>
       </c>
       <c r="R9" t="n">
-        <v>6837047</v>
+        <v>6837020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118614092</v>
+        <v>118614097</v>
       </c>
       <c r="B10" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455960</v>
+        <v>456025</v>
       </c>
       <c r="R10" t="n">
-        <v>6837047</v>
+        <v>6836910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118614086</v>
+        <v>118614089</v>
       </c>
       <c r="B11" t="n">
-        <v>78583</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,34 +1609,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455907</v>
+        <v>456021</v>
       </c>
       <c r="R11" t="n">
-        <v>6837012</v>
+        <v>6837003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,6 +1677,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118614078</v>
+        <v>118614077</v>
       </c>
       <c r="B12" t="n">
         <v>79102</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455889</v>
+        <v>456008</v>
       </c>
       <c r="R12" t="n">
-        <v>6836903</v>
+        <v>6836969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118614098</v>
+        <v>118614102</v>
       </c>
       <c r="B13" t="n">
         <v>78220</v>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455984</v>
+        <v>455889</v>
       </c>
       <c r="R13" t="n">
-        <v>6836875</v>
+        <v>6836903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118614109</v>
+        <v>118614081</v>
       </c>
       <c r="B14" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456008</v>
+        <v>455942</v>
       </c>
       <c r="R14" t="n">
-        <v>6837047</v>
+        <v>6837031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118614096</v>
+        <v>118614087</v>
       </c>
       <c r="B15" t="n">
-        <v>78220</v>
+        <v>78583</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456010</v>
+        <v>455959</v>
       </c>
       <c r="R15" t="n">
-        <v>6836965</v>
+        <v>6837052</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118614084</v>
+        <v>118614101</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456032</v>
+        <v>455923</v>
       </c>
       <c r="R16" t="n">
-        <v>6836895</v>
+        <v>6836875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118614097</v>
+        <v>118614108</v>
       </c>
       <c r="B17" t="n">
         <v>78220</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456025</v>
+        <v>455960</v>
       </c>
       <c r="R17" t="n">
-        <v>6836910</v>
+        <v>6837047</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118614102</v>
+        <v>118614078</v>
       </c>
       <c r="B18" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,21 +2336,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118614076</v>
+        <v>118614091</v>
       </c>
       <c r="B19" t="n">
-        <v>78518</v>
+        <v>78221</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456018</v>
+        <v>455881</v>
       </c>
       <c r="R19" t="n">
-        <v>6837020</v>
+        <v>6836923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118614107</v>
+        <v>118614079</v>
       </c>
       <c r="B20" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,21 +2540,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455942</v>
+        <v>455886</v>
       </c>
       <c r="R20" t="n">
-        <v>6836999</v>
+        <v>6836900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118614083</v>
+        <v>118614082</v>
       </c>
       <c r="B21" t="n">
         <v>79102</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455947</v>
+        <v>455942</v>
       </c>
       <c r="R21" t="n">
-        <v>6837045</v>
+        <v>6837052</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118614082</v>
+        <v>118614093</v>
       </c>
       <c r="B22" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455942</v>
+        <v>456008</v>
       </c>
       <c r="R22" t="n">
-        <v>6837052</v>
+        <v>6837047</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118614105</v>
+        <v>118614110</v>
       </c>
       <c r="B24" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455881</v>
+        <v>456021</v>
       </c>
       <c r="R24" t="n">
-        <v>6836923</v>
+        <v>6836968</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118614077</v>
+        <v>118614106</v>
       </c>
       <c r="B25" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456008</v>
+        <v>455886</v>
       </c>
       <c r="R25" t="n">
-        <v>6836969</v>
+        <v>6836975</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118614101</v>
+        <v>118614086</v>
       </c>
       <c r="B26" t="n">
-        <v>78220</v>
+        <v>78583</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455923</v>
+        <v>455907</v>
       </c>
       <c r="R26" t="n">
-        <v>6836875</v>
+        <v>6837012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118614099</v>
+        <v>118614083</v>
       </c>
       <c r="B27" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455969</v>
+        <v>455947</v>
       </c>
       <c r="R27" t="n">
-        <v>6836868</v>
+        <v>6837045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118614090</v>
+        <v>118614105</v>
       </c>
       <c r="B28" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455935</v>
+        <v>455881</v>
       </c>
       <c r="R28" t="n">
-        <v>6836857</v>
+        <v>6836923</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118614095</v>
+        <v>118614098</v>
       </c>
       <c r="B29" t="n">
         <v>78220</v>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455985</v>
+        <v>455984</v>
       </c>
       <c r="R29" t="n">
-        <v>6836979</v>
+        <v>6836875</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118614108</v>
+        <v>118614107</v>
       </c>
       <c r="B30" t="n">
         <v>78220</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455960</v>
+        <v>455942</v>
       </c>
       <c r="R30" t="n">
-        <v>6837047</v>
+        <v>6836999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,7 +3646,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118614100</v>
+        <v>118614109</v>
       </c>
       <c r="B31" t="n">
         <v>78220</v>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455939</v>
+        <v>456008</v>
       </c>
       <c r="R31" t="n">
-        <v>6836859</v>
+        <v>6837047</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118614088</v>
+        <v>118614100</v>
       </c>
       <c r="B32" t="n">
-        <v>57443</v>
+        <v>78220</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455935</v>
+        <v>455939</v>
       </c>
       <c r="R32" t="n">
-        <v>6836858</v>
+        <v>6836859</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118614106</v>
+        <v>118614103</v>
       </c>
       <c r="B33" t="n">
         <v>78220</v>
@@ -3893,7 +3893,7 @@
         <v>455886</v>
       </c>
       <c r="R33" t="n">
-        <v>6836975</v>
+        <v>6836900</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118614091</v>
+        <v>118614090</v>
       </c>
       <c r="B34" t="n">
         <v>78221</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455881</v>
+        <v>455935</v>
       </c>
       <c r="R34" t="n">
-        <v>6836923</v>
+        <v>6836857</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118727558</v>
+        <v>118727521</v>
       </c>
       <c r="B35" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4070,45 +4070,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456036</v>
+        <v>455919</v>
       </c>
       <c r="R35" t="n">
-        <v>6836794</v>
+        <v>6836937</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,7 +4139,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4168,10 +4157,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118727633</v>
+        <v>118727537</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,34 +4173,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455917</v>
+        <v>456027</v>
       </c>
       <c r="R36" t="n">
-        <v>6836957</v>
+        <v>6836806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118727608</v>
+        <v>118727662</v>
       </c>
       <c r="B37" t="n">
-        <v>78220</v>
+        <v>77416</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4276,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456041</v>
+        <v>455700</v>
       </c>
       <c r="R37" t="n">
-        <v>6836795</v>
+        <v>6837084</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118727581</v>
+        <v>118727544</v>
       </c>
       <c r="B38" t="n">
-        <v>57290</v>
+        <v>79102</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,42 +4378,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455926</v>
+        <v>456065</v>
       </c>
       <c r="R38" t="n">
-        <v>6836949</v>
+        <v>6836867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4439,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118727506</v>
+        <v>118727617</v>
       </c>
       <c r="B39" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4503,35 +4481,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455726</v>
+        <v>455720</v>
       </c>
       <c r="R39" t="n">
-        <v>6837083</v>
+        <v>6837077</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727655</v>
+        <v>118727596</v>
       </c>
       <c r="B40" t="n">
-        <v>78129</v>
+        <v>78221</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4606,21 +4583,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4630,10 +4607,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455973</v>
+        <v>455956</v>
       </c>
       <c r="R40" t="n">
-        <v>6836775</v>
+        <v>6837009</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727612</v>
+        <v>118727588</v>
       </c>
       <c r="B41" t="n">
-        <v>90654</v>
+        <v>78221</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,25 +4681,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4732,10 +4709,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455930</v>
+        <v>455938</v>
       </c>
       <c r="R41" t="n">
-        <v>6836843</v>
+        <v>6836861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,10 +4771,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727648</v>
+        <v>118727556</v>
       </c>
       <c r="B42" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,34 +4787,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456055</v>
+        <v>456028</v>
       </c>
       <c r="R42" t="n">
-        <v>6836875</v>
+        <v>6836813</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4896,10 +4874,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727529</v>
+        <v>118727554</v>
       </c>
       <c r="B43" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,21 +4890,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4915,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455885</v>
+        <v>456036</v>
       </c>
       <c r="R43" t="n">
-        <v>6836757</v>
+        <v>6836795</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4977,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727520</v>
+        <v>118727612</v>
       </c>
       <c r="B44" t="n">
-        <v>79102</v>
+        <v>90654</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,39 +4989,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455867</v>
+        <v>455930</v>
       </c>
       <c r="R44" t="n">
-        <v>6836942</v>
+        <v>6836843</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5102,10 +5079,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727537</v>
+        <v>118727546</v>
       </c>
       <c r="B45" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,21 +5095,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5143,10 +5120,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456027</v>
+        <v>455932</v>
       </c>
       <c r="R45" t="n">
-        <v>6836806</v>
+        <v>6836858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5205,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727625</v>
+        <v>118727629</v>
       </c>
       <c r="B46" t="n">
         <v>78484</v>
@@ -5245,10 +5222,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455868</v>
+        <v>455870</v>
       </c>
       <c r="R46" t="n">
-        <v>6837146</v>
+        <v>6837153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,10 +5284,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727609</v>
+        <v>118727587</v>
       </c>
       <c r="B47" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5323,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5347,10 +5324,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456053</v>
+        <v>455933</v>
       </c>
       <c r="R47" t="n">
-        <v>6836858</v>
+        <v>6836859</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5409,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118727549</v>
+        <v>118727526</v>
       </c>
       <c r="B48" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5425,21 +5402,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455956</v>
+        <v>455943</v>
       </c>
       <c r="R48" t="n">
-        <v>6836745</v>
+        <v>6836795</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118727587</v>
+        <v>118727543</v>
       </c>
       <c r="B49" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5528,34 +5505,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455933</v>
+        <v>456050</v>
       </c>
       <c r="R49" t="n">
-        <v>6836859</v>
+        <v>6836858</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5614,10 +5592,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118727547</v>
+        <v>118727604</v>
       </c>
       <c r="B50" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5630,35 +5608,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455904</v>
+        <v>455931</v>
       </c>
       <c r="R50" t="n">
-        <v>6836778</v>
+        <v>6836858</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5717,10 +5694,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118727511</v>
+        <v>118727531</v>
       </c>
       <c r="B51" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5733,21 +5710,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5758,10 +5735,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455951</v>
+        <v>455918</v>
       </c>
       <c r="R51" t="n">
-        <v>6836741</v>
+        <v>6836750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,10 +5797,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118727620</v>
+        <v>118727507</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5836,34 +5813,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455733</v>
+        <v>455726</v>
       </c>
       <c r="R52" t="n">
-        <v>6837103</v>
+        <v>6837099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,10 +5900,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118727653</v>
+        <v>118727560</v>
       </c>
       <c r="B53" t="n">
-        <v>94513</v>
+        <v>78583</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5934,38 +5912,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2170</v>
+        <v>967</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456022</v>
+        <v>455904</v>
       </c>
       <c r="R53" t="n">
-        <v>6836970</v>
+        <v>6836777</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,6 +5995,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6024,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118727638</v>
+        <v>118727511</v>
       </c>
       <c r="B54" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6040,34 +6030,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455933</v>
+        <v>455951</v>
       </c>
       <c r="R54" t="n">
-        <v>6836917</v>
+        <v>6836741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6126,10 +6117,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118727541</v>
+        <v>118727513</v>
       </c>
       <c r="B55" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6142,21 +6133,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6167,10 +6158,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456048</v>
+        <v>455971</v>
       </c>
       <c r="R55" t="n">
-        <v>6836813</v>
+        <v>6836747</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6229,10 +6220,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118727528</v>
+        <v>118727503</v>
       </c>
       <c r="B56" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6245,35 +6236,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455898</v>
+        <v>456028</v>
       </c>
       <c r="R56" t="n">
-        <v>6836767</v>
+        <v>6836799</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6332,7 +6322,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118727538</v>
+        <v>118727527</v>
       </c>
       <c r="B57" t="n">
         <v>79102</v>
@@ -6373,10 +6363,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456041</v>
+        <v>455903</v>
       </c>
       <c r="R57" t="n">
-        <v>6836794</v>
+        <v>6836778</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6435,10 +6425,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118727603</v>
+        <v>118727593</v>
       </c>
       <c r="B58" t="n">
-        <v>80441</v>
+        <v>78221</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6451,21 +6441,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6475,10 +6465,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456024</v>
+        <v>456027</v>
       </c>
       <c r="R58" t="n">
-        <v>6836818</v>
+        <v>6836806</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6537,10 +6527,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118727617</v>
+        <v>118727609</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6553,21 +6543,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6577,10 +6567,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455720</v>
+        <v>456053</v>
       </c>
       <c r="R59" t="n">
-        <v>6837077</v>
+        <v>6836858</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6639,10 +6629,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118727665</v>
+        <v>118727640</v>
       </c>
       <c r="B60" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6655,21 +6645,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6679,10 +6669,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455701</v>
+        <v>455987</v>
       </c>
       <c r="R60" t="n">
-        <v>6837084</v>
+        <v>6836765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6741,7 +6731,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118727619</v>
+        <v>118727633</v>
       </c>
       <c r="B61" t="n">
         <v>78484</v>
@@ -6781,10 +6771,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455726</v>
+        <v>455917</v>
       </c>
       <c r="R61" t="n">
-        <v>6837099</v>
+        <v>6836957</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,10 +6833,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118727582</v>
+        <v>118727549</v>
       </c>
       <c r="B62" t="n">
-        <v>57290</v>
+        <v>79073</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6859,42 +6849,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455915</v>
+        <v>455956</v>
       </c>
       <c r="R62" t="n">
-        <v>6836954</v>
+        <v>6836745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6927,11 +6910,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6958,10 +6936,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118727545</v>
+        <v>118727598</v>
       </c>
       <c r="B63" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,35 +6952,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455700</v>
+        <v>455878</v>
       </c>
       <c r="R63" t="n">
-        <v>6837083</v>
+        <v>6836925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7061,10 +7038,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118727556</v>
+        <v>118727651</v>
       </c>
       <c r="B64" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7073,39 +7050,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456028</v>
+        <v>455972</v>
       </c>
       <c r="R64" t="n">
-        <v>6836813</v>
+        <v>6836775</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,10 +7140,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727517</v>
+        <v>118727600</v>
       </c>
       <c r="B65" t="n">
-        <v>79102</v>
+        <v>80441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7180,35 +7156,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455986</v>
+        <v>455702</v>
       </c>
       <c r="R65" t="n">
-        <v>6836980</v>
+        <v>6837084</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7267,10 +7242,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118727527</v>
+        <v>118727603</v>
       </c>
       <c r="B66" t="n">
-        <v>79102</v>
+        <v>80441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7283,35 +7258,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455903</v>
+        <v>456024</v>
       </c>
       <c r="R66" t="n">
-        <v>6836778</v>
+        <v>6836818</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,10 +7344,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118727583</v>
+        <v>118727525</v>
       </c>
       <c r="B67" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7386,34 +7360,35 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456050</v>
+        <v>455924</v>
       </c>
       <c r="R67" t="n">
-        <v>6836858</v>
+        <v>6836801</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7447,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118727598</v>
+        <v>118727648</v>
       </c>
       <c r="B68" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7488,21 +7463,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7512,10 +7487,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455878</v>
+        <v>456055</v>
       </c>
       <c r="R68" t="n">
-        <v>6836925</v>
+        <v>6836875</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,10 +7549,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727550</v>
+        <v>118727630</v>
       </c>
       <c r="B69" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7590,35 +7565,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455970</v>
+        <v>455860</v>
       </c>
       <c r="R69" t="n">
-        <v>6836763</v>
+        <v>6837129</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,10 +7651,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727585</v>
+        <v>118727639</v>
       </c>
       <c r="B70" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,21 +7667,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7691,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455930</v>
+        <v>455967</v>
       </c>
       <c r="R70" t="n">
-        <v>6836897</v>
+        <v>6836746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7779,10 +7753,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727539</v>
+        <v>118727618</v>
       </c>
       <c r="B71" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7795,35 +7769,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456035</v>
+        <v>455724</v>
       </c>
       <c r="R71" t="n">
-        <v>6836794</v>
+        <v>6837080</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7882,10 +7855,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727635</v>
+        <v>118727519</v>
       </c>
       <c r="B72" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7898,34 +7871,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455915</v>
+        <v>455850</v>
       </c>
       <c r="R72" t="n">
-        <v>6836927</v>
+        <v>6837094</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7984,10 +7958,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727636</v>
+        <v>118727529</v>
       </c>
       <c r="B73" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8000,34 +7974,35 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455925</v>
+        <v>455885</v>
       </c>
       <c r="R73" t="n">
-        <v>6836919</v>
+        <v>6836757</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8086,7 +8061,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118727618</v>
+        <v>118727627</v>
       </c>
       <c r="B74" t="n">
         <v>78484</v>
@@ -8126,10 +8101,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455724</v>
+        <v>455891</v>
       </c>
       <c r="R74" t="n">
-        <v>6837080</v>
+        <v>6836950</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,10 +8265,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118727507</v>
+        <v>118727632</v>
       </c>
       <c r="B76" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8306,35 +8281,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455726</v>
+        <v>455916</v>
       </c>
       <c r="R76" t="n">
-        <v>6837099</v>
+        <v>6836963</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8393,10 +8367,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118727503</v>
+        <v>118727583</v>
       </c>
       <c r="B77" t="n">
-        <v>78518</v>
+        <v>78221</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8409,21 +8383,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8433,10 +8407,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456028</v>
+        <v>456050</v>
       </c>
       <c r="R77" t="n">
-        <v>6836799</v>
+        <v>6836858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8495,7 +8469,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118727597</v>
+        <v>118727595</v>
       </c>
       <c r="B78" t="n">
         <v>78221</v>
@@ -8535,10 +8509,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455943</v>
+        <v>455986</v>
       </c>
       <c r="R78" t="n">
-        <v>6836998</v>
+        <v>6836980</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8597,7 +8571,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118727594</v>
+        <v>118727591</v>
       </c>
       <c r="B79" t="n">
         <v>78221</v>
@@ -8637,10 +8611,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>456008</v>
+        <v>455924</v>
       </c>
       <c r="R79" t="n">
-        <v>6836969</v>
+        <v>6836800</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8699,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118727554</v>
+        <v>118727610</v>
       </c>
       <c r="B80" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8715,35 +8689,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456036</v>
+        <v>455955</v>
       </c>
       <c r="R80" t="n">
-        <v>6836795</v>
+        <v>6837009</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8802,10 +8775,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118727502</v>
+        <v>118727528</v>
       </c>
       <c r="B81" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8818,34 +8791,35 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>456023</v>
+        <v>455898</v>
       </c>
       <c r="R81" t="n">
-        <v>6836783</v>
+        <v>6836767</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8904,10 +8878,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118727624</v>
+        <v>118727582</v>
       </c>
       <c r="B82" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8920,34 +8894,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>455844</v>
+        <v>455915</v>
       </c>
       <c r="R82" t="n">
-        <v>6837118</v>
+        <v>6836954</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8980,6 +8962,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9006,10 +8993,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118727667</v>
+        <v>118727517</v>
       </c>
       <c r="B83" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9022,34 +9009,35 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>456035</v>
+        <v>455986</v>
       </c>
       <c r="R83" t="n">
-        <v>6836796</v>
+        <v>6836980</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9210,10 +9198,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118727611</v>
+        <v>118727558</v>
       </c>
       <c r="B85" t="n">
-        <v>90654</v>
+        <v>78583</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9222,38 +9210,49 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1503</v>
+        <v>967</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>455716</v>
+        <v>456036</v>
       </c>
       <c r="R85" t="n">
-        <v>6837046</v>
+        <v>6836794</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9294,6 +9293,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727593</v>
+        <v>118727532</v>
       </c>
       <c r="B87" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9430,34 +9430,35 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>456027</v>
+        <v>455926</v>
       </c>
       <c r="R87" t="n">
-        <v>6836806</v>
+        <v>6836752</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9516,7 +9517,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727523</v>
+        <v>118727530</v>
       </c>
       <c r="B88" t="n">
         <v>79102</v>
@@ -9557,10 +9558,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455933</v>
+        <v>455892</v>
       </c>
       <c r="R88" t="n">
-        <v>6836859</v>
+        <v>6836753</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9619,7 +9620,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118727639</v>
+        <v>118727636</v>
       </c>
       <c r="B89" t="n">
         <v>78484</v>
@@ -9659,10 +9660,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455967</v>
+        <v>455925</v>
       </c>
       <c r="R89" t="n">
-        <v>6836746</v>
+        <v>6836919</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9721,10 +9722,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118727627</v>
+        <v>118727592</v>
       </c>
       <c r="B90" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9737,21 +9738,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9761,10 +9762,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455891</v>
+        <v>456025</v>
       </c>
       <c r="R90" t="n">
-        <v>6836950</v>
+        <v>6836800</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9823,10 +9824,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118727660</v>
+        <v>118727631</v>
       </c>
       <c r="B91" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9839,21 +9840,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9863,10 +9864,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>456065</v>
+        <v>455914</v>
       </c>
       <c r="R91" t="n">
-        <v>6836867</v>
+        <v>6836965</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9925,10 +9926,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118727519</v>
+        <v>118727545</v>
       </c>
       <c r="B92" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9941,21 +9942,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9966,10 +9967,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>455850</v>
+        <v>455700</v>
       </c>
       <c r="R92" t="n">
-        <v>6837094</v>
+        <v>6837083</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10028,10 +10029,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118727607</v>
+        <v>118727590</v>
       </c>
       <c r="B93" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10044,21 +10045,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10068,10 +10069,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>456027</v>
+        <v>455955</v>
       </c>
       <c r="R93" t="n">
-        <v>6836806</v>
+        <v>6836833</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10130,10 +10131,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118727565</v>
+        <v>118727502</v>
       </c>
       <c r="B94" t="n">
-        <v>57443</v>
+        <v>78518</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10146,21 +10147,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10170,10 +10171,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>455864</v>
+        <v>456023</v>
       </c>
       <c r="R94" t="n">
-        <v>6837158</v>
+        <v>6836783</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10232,10 +10233,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118727553</v>
+        <v>118727508</v>
       </c>
       <c r="B95" t="n">
-        <v>79073</v>
+        <v>78518</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10248,21 +10249,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10273,10 +10274,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>456026</v>
+        <v>455765</v>
       </c>
       <c r="R95" t="n">
-        <v>6836798</v>
+        <v>6837108</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10335,10 +10336,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118727508</v>
+        <v>118727667</v>
       </c>
       <c r="B96" t="n">
-        <v>78518</v>
+        <v>77868</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10351,35 +10352,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455765</v>
+        <v>456035</v>
       </c>
       <c r="R96" t="n">
-        <v>6837108</v>
+        <v>6836796</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10438,10 +10438,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118727532</v>
+        <v>118727506</v>
       </c>
       <c r="B97" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10479,10 +10479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455926</v>
+        <v>455726</v>
       </c>
       <c r="R97" t="n">
-        <v>6836752</v>
+        <v>6837083</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10541,10 +10541,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118727604</v>
+        <v>118727611</v>
       </c>
       <c r="B98" t="n">
-        <v>78220</v>
+        <v>90654</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10553,25 +10553,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455931</v>
+        <v>455716</v>
       </c>
       <c r="R98" t="n">
-        <v>6836858</v>
+        <v>6837046</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10643,10 +10643,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118727595</v>
+        <v>118727579</v>
       </c>
       <c r="B99" t="n">
-        <v>78221</v>
+        <v>78573</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10655,25 +10655,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455986</v>
+        <v>455885</v>
       </c>
       <c r="R99" t="n">
-        <v>6836980</v>
+        <v>6836936</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10745,10 +10745,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118727546</v>
+        <v>118727542</v>
       </c>
       <c r="B100" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10761,21 +10761,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455932</v>
+        <v>456022</v>
       </c>
       <c r="R100" t="n">
-        <v>6836858</v>
+        <v>6836819</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118727640</v>
+        <v>118727538</v>
       </c>
       <c r="B101" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10864,34 +10864,35 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455987</v>
+        <v>456041</v>
       </c>
       <c r="R101" t="n">
-        <v>6836765</v>
+        <v>6836794</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10950,10 +10951,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118727610</v>
+        <v>118727626</v>
       </c>
       <c r="B102" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10966,21 +10967,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10990,10 +10991,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455955</v>
+        <v>455897</v>
       </c>
       <c r="R102" t="n">
-        <v>6837009</v>
+        <v>6836935</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11052,10 +11053,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118727606</v>
+        <v>118727619</v>
       </c>
       <c r="B103" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11068,21 +11069,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11092,10 +11093,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456025</v>
+        <v>455726</v>
       </c>
       <c r="R103" t="n">
-        <v>6836801</v>
+        <v>6837099</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11154,10 +11155,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118727631</v>
+        <v>118727608</v>
       </c>
       <c r="B104" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11170,21 +11171,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11194,10 +11195,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>455914</v>
+        <v>456041</v>
       </c>
       <c r="R104" t="n">
-        <v>6836965</v>
+        <v>6836795</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11256,10 +11257,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118727658</v>
+        <v>118727606</v>
       </c>
       <c r="B105" t="n">
-        <v>78129</v>
+        <v>78220</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11272,21 +11273,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11296,10 +11297,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455957</v>
+        <v>456025</v>
       </c>
       <c r="R105" t="n">
-        <v>6836744</v>
+        <v>6836801</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,10 +11359,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118727586</v>
+        <v>118727565</v>
       </c>
       <c r="B106" t="n">
-        <v>78221</v>
+        <v>57443</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11374,21 +11375,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11398,10 +11399,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455865</v>
+        <v>455864</v>
       </c>
       <c r="R106" t="n">
-        <v>6836943</v>
+        <v>6837158</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11460,10 +11461,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118727560</v>
+        <v>118727653</v>
       </c>
       <c r="B107" t="n">
-        <v>78583</v>
+        <v>94513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11472,49 +11473,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>967</v>
+        <v>2170</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455904</v>
+        <v>456022</v>
       </c>
       <c r="R107" t="n">
-        <v>6836777</v>
+        <v>6836970</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11555,7 +11545,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11574,10 +11563,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118727521</v>
+        <v>118727586</v>
       </c>
       <c r="B108" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11590,35 +11579,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>455919</v>
+        <v>455865</v>
       </c>
       <c r="R108" t="n">
-        <v>6836937</v>
+        <v>6836943</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11677,10 +11665,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118727530</v>
+        <v>118727597</v>
       </c>
       <c r="B109" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11693,35 +11681,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>455892</v>
+        <v>455943</v>
       </c>
       <c r="R109" t="n">
-        <v>6836753</v>
+        <v>6836998</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11780,10 +11767,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727510</v>
+        <v>118727594</v>
       </c>
       <c r="B110" t="n">
-        <v>78518</v>
+        <v>78221</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11796,32 +11783,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>455912</v>
+        <v>456008</v>
       </c>
       <c r="R110" t="n">
         <v>6836969</v>
@@ -11883,10 +11869,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727600</v>
+        <v>118727658</v>
       </c>
       <c r="B111" t="n">
-        <v>80441</v>
+        <v>78129</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11899,21 +11885,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11923,10 +11909,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455702</v>
+        <v>455957</v>
       </c>
       <c r="R111" t="n">
-        <v>6837084</v>
+        <v>6836744</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11985,10 +11971,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727557</v>
+        <v>118727539</v>
       </c>
       <c r="B112" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12001,21 +11987,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12026,10 +12012,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456053</v>
+        <v>456035</v>
       </c>
       <c r="R112" t="n">
-        <v>6836858</v>
+        <v>6836794</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12088,10 +12074,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727590</v>
+        <v>118727625</v>
       </c>
       <c r="B113" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12104,21 +12090,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12128,10 +12114,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455955</v>
+        <v>455868</v>
       </c>
       <c r="R113" t="n">
-        <v>6836833</v>
+        <v>6837146</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12190,10 +12176,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727668</v>
+        <v>118727635</v>
       </c>
       <c r="B114" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12206,21 +12192,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12230,10 +12216,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>456028</v>
+        <v>455915</v>
       </c>
       <c r="R114" t="n">
-        <v>6836814</v>
+        <v>6836927</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12292,10 +12278,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727542</v>
+        <v>118727599</v>
       </c>
       <c r="B115" t="n">
-        <v>79102</v>
+        <v>90966</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12308,35 +12294,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>5467</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456022</v>
+        <v>455957</v>
       </c>
       <c r="R115" t="n">
-        <v>6836819</v>
+        <v>6836745</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12395,10 +12380,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727524</v>
+        <v>118727620</v>
       </c>
       <c r="B116" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12411,35 +12396,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455955</v>
+        <v>455733</v>
       </c>
       <c r="R116" t="n">
-        <v>6836833</v>
+        <v>6837103</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12498,10 +12482,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727629</v>
+        <v>118727547</v>
       </c>
       <c r="B117" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12514,34 +12498,35 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455870</v>
+        <v>455904</v>
       </c>
       <c r="R117" t="n">
-        <v>6837153</v>
+        <v>6836778</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12600,10 +12585,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727622</v>
+        <v>118727585</v>
       </c>
       <c r="B118" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12616,21 +12601,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12640,10 +12625,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455747</v>
+        <v>455930</v>
       </c>
       <c r="R118" t="n">
-        <v>6837101</v>
+        <v>6836897</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12702,10 +12687,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727623</v>
+        <v>118727581</v>
       </c>
       <c r="B119" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,34 +12703,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455802</v>
+        <v>455926</v>
       </c>
       <c r="R119" t="n">
-        <v>6837089</v>
+        <v>6836949</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12778,6 +12771,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12804,10 +12802,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727548</v>
+        <v>118727601</v>
       </c>
       <c r="B120" t="n">
-        <v>79073</v>
+        <v>80441</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,35 +12818,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455926</v>
+        <v>455913</v>
       </c>
       <c r="R120" t="n">
-        <v>6836752</v>
+        <v>6836820</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12907,10 +12904,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118727584</v>
+        <v>118727523</v>
       </c>
       <c r="B121" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12923,34 +12920,35 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>456053</v>
+        <v>455933</v>
       </c>
       <c r="R121" t="n">
-        <v>6836858</v>
+        <v>6836859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13009,10 +13007,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118727591</v>
+        <v>118727624</v>
       </c>
       <c r="B122" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13025,21 +13023,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13049,10 +13047,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455924</v>
+        <v>455844</v>
       </c>
       <c r="R122" t="n">
-        <v>6836800</v>
+        <v>6837118</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13111,10 +13109,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118727651</v>
+        <v>118727510</v>
       </c>
       <c r="B123" t="n">
-        <v>90749</v>
+        <v>78518</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13123,38 +13121,39 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>455972</v>
+        <v>455912</v>
       </c>
       <c r="R123" t="n">
-        <v>6836775</v>
+        <v>6836969</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13213,10 +13212,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118727630</v>
+        <v>118727652</v>
       </c>
       <c r="B124" t="n">
-        <v>78484</v>
+        <v>94513</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13225,25 +13224,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13253,10 +13252,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>455860</v>
+        <v>455841</v>
       </c>
       <c r="R124" t="n">
-        <v>6837129</v>
+        <v>6837101</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13315,10 +13314,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118727601</v>
+        <v>118727541</v>
       </c>
       <c r="B125" t="n">
-        <v>80441</v>
+        <v>79102</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13331,34 +13330,35 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>455913</v>
+        <v>456048</v>
       </c>
       <c r="R125" t="n">
-        <v>6836820</v>
+        <v>6836813</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118727543</v>
+        <v>118727524</v>
       </c>
       <c r="B126" t="n">
         <v>79102</v>
@@ -13458,10 +13458,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>456050</v>
+        <v>455955</v>
       </c>
       <c r="R126" t="n">
-        <v>6836858</v>
+        <v>6836833</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13520,10 +13520,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118727579</v>
+        <v>118727533</v>
       </c>
       <c r="B127" t="n">
-        <v>78573</v>
+        <v>79102</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13532,38 +13532,39 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455885</v>
+        <v>455956</v>
       </c>
       <c r="R127" t="n">
-        <v>6836936</v>
+        <v>6836745</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13622,10 +13623,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118727525</v>
+        <v>118727668</v>
       </c>
       <c r="B128" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13638,35 +13639,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>455924</v>
+        <v>456028</v>
       </c>
       <c r="R128" t="n">
-        <v>6836801</v>
+        <v>6836814</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13725,10 +13725,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118727599</v>
+        <v>118727557</v>
       </c>
       <c r="B129" t="n">
-        <v>90966</v>
+        <v>79073</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13741,34 +13741,35 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5467</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>455957</v>
+        <v>456053</v>
       </c>
       <c r="R129" t="n">
-        <v>6836745</v>
+        <v>6836858</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13827,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118727596</v>
+        <v>118727561</v>
       </c>
       <c r="B130" t="n">
-        <v>78221</v>
+        <v>78583</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13843,21 +13844,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13867,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455956</v>
+        <v>455930</v>
       </c>
       <c r="R130" t="n">
-        <v>6837009</v>
+        <v>6836890</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13929,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118727561</v>
+        <v>118727520</v>
       </c>
       <c r="B131" t="n">
-        <v>78583</v>
+        <v>79102</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13945,34 +13946,35 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455930</v>
+        <v>455867</v>
       </c>
       <c r="R131" t="n">
-        <v>6836890</v>
+        <v>6836942</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14031,10 +14033,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118727518</v>
+        <v>118727665</v>
       </c>
       <c r="B132" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14047,35 +14049,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455952</v>
+        <v>455701</v>
       </c>
       <c r="R132" t="n">
-        <v>6836992</v>
+        <v>6837084</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14134,10 +14135,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118727544</v>
+        <v>118727638</v>
       </c>
       <c r="B133" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14150,35 +14151,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>456065</v>
+        <v>455933</v>
       </c>
       <c r="R133" t="n">
-        <v>6836867</v>
+        <v>6836917</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14237,10 +14237,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118727533</v>
+        <v>118727607</v>
       </c>
       <c r="B134" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14253,35 +14253,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455956</v>
+        <v>456027</v>
       </c>
       <c r="R134" t="n">
-        <v>6836745</v>
+        <v>6836806</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14340,10 +14339,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118727662</v>
+        <v>118727623</v>
       </c>
       <c r="B135" t="n">
-        <v>77416</v>
+        <v>78484</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14356,21 +14355,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14380,10 +14379,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455700</v>
+        <v>455802</v>
       </c>
       <c r="R135" t="n">
-        <v>6837084</v>
+        <v>6837089</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14442,10 +14441,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118727513</v>
+        <v>118727548</v>
       </c>
       <c r="B136" t="n">
-        <v>78518</v>
+        <v>79073</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14458,21 +14457,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14483,10 +14482,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455971</v>
+        <v>455926</v>
       </c>
       <c r="R136" t="n">
-        <v>6836747</v>
+        <v>6836752</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14545,7 +14544,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118727592</v>
+        <v>118727584</v>
       </c>
       <c r="B137" t="n">
         <v>78221</v>
@@ -14585,10 +14584,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456025</v>
+        <v>456053</v>
       </c>
       <c r="R137" t="n">
-        <v>6836800</v>
+        <v>6836858</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14647,10 +14646,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118727588</v>
+        <v>118727550</v>
       </c>
       <c r="B138" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14663,34 +14662,35 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455938</v>
+        <v>455970</v>
       </c>
       <c r="R138" t="n">
-        <v>6836861</v>
+        <v>6836763</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14749,10 +14749,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118727632</v>
+        <v>118727553</v>
       </c>
       <c r="B139" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14765,34 +14765,35 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>455916</v>
+        <v>456026</v>
       </c>
       <c r="R139" t="n">
-        <v>6836963</v>
+        <v>6836798</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14851,7 +14852,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118727626</v>
+        <v>118727622</v>
       </c>
       <c r="B140" t="n">
         <v>78484</v>
@@ -14891,10 +14892,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455897</v>
+        <v>455747</v>
       </c>
       <c r="R140" t="n">
-        <v>6836935</v>
+        <v>6837101</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14953,10 +14954,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118727652</v>
+        <v>118727655</v>
       </c>
       <c r="B141" t="n">
-        <v>94513</v>
+        <v>78129</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14965,25 +14966,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14993,10 +14994,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455841</v>
+        <v>455973</v>
       </c>
       <c r="R141" t="n">
-        <v>6837101</v>
+        <v>6836775</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15055,10 +15056,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118727526</v>
+        <v>118727660</v>
       </c>
       <c r="B142" t="n">
-        <v>79102</v>
+        <v>78129</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15071,35 +15072,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455943</v>
+        <v>456065</v>
       </c>
       <c r="R142" t="n">
-        <v>6836795</v>
+        <v>6836867</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15158,7 +15158,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118727531</v>
+        <v>118727518</v>
       </c>
       <c r="B143" t="n">
         <v>79102</v>
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455918</v>
+        <v>455952</v>
       </c>
       <c r="R143" t="n">
-        <v>6836750</v>
+        <v>6836992</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118614099</v>
+        <v>118614101</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455969</v>
+        <v>455923</v>
       </c>
       <c r="R2" t="n">
-        <v>6836868</v>
+        <v>6836875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118614084</v>
+        <v>118614107</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456032</v>
+        <v>455942</v>
       </c>
       <c r="R3" t="n">
-        <v>6836895</v>
+        <v>6836999</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>118614096</v>
       </c>
       <c r="B4" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118614092</v>
+        <v>118614106</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455960</v>
+        <v>455886</v>
       </c>
       <c r="R5" t="n">
-        <v>6837047</v>
+        <v>6836975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614088</v>
+        <v>118614091</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455935</v>
+        <v>455881</v>
       </c>
       <c r="R6" t="n">
-        <v>6836858</v>
+        <v>6836923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614111</v>
+        <v>118614076</v>
       </c>
       <c r="B7" t="n">
-        <v>78129</v>
+        <v>78525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455971</v>
+        <v>456018</v>
       </c>
       <c r="R7" t="n">
-        <v>6837047</v>
+        <v>6837020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118614095</v>
+        <v>118614099</v>
       </c>
       <c r="B8" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455985</v>
+        <v>455969</v>
       </c>
       <c r="R8" t="n">
-        <v>6836979</v>
+        <v>6836868</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118614076</v>
+        <v>118614077</v>
       </c>
       <c r="B9" t="n">
-        <v>78518</v>
+        <v>79109</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456018</v>
+        <v>456008</v>
       </c>
       <c r="R9" t="n">
-        <v>6837020</v>
+        <v>6836969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118614097</v>
+        <v>118614089</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456025</v>
+        <v>456021</v>
       </c>
       <c r="R10" t="n">
-        <v>6836910</v>
+        <v>6837003</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1575,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118614089</v>
+        <v>118614097</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>78227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,42 +1622,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456021</v>
+        <v>456025</v>
       </c>
       <c r="R11" t="n">
-        <v>6837003</v>
+        <v>6836910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,11 +1682,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118614077</v>
+        <v>118614083</v>
       </c>
       <c r="B12" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456008</v>
+        <v>455947</v>
       </c>
       <c r="R12" t="n">
-        <v>6836969</v>
+        <v>6837045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118614102</v>
+        <v>118614110</v>
       </c>
       <c r="B13" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455889</v>
+        <v>456021</v>
       </c>
       <c r="R13" t="n">
-        <v>6836903</v>
+        <v>6836968</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118614081</v>
+        <v>118614103</v>
       </c>
       <c r="B14" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455942</v>
+        <v>455886</v>
       </c>
       <c r="R14" t="n">
-        <v>6837031</v>
+        <v>6836900</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118614087</v>
+        <v>118614081</v>
       </c>
       <c r="B15" t="n">
-        <v>78583</v>
+        <v>79109</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455959</v>
+        <v>455942</v>
       </c>
       <c r="R15" t="n">
-        <v>6837052</v>
+        <v>6837031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118614101</v>
+        <v>118614092</v>
       </c>
       <c r="B16" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455923</v>
+        <v>455960</v>
       </c>
       <c r="R16" t="n">
-        <v>6836875</v>
+        <v>6837047</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118614108</v>
+        <v>118614084</v>
       </c>
       <c r="B17" t="n">
-        <v>78220</v>
+        <v>79080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455960</v>
+        <v>456032</v>
       </c>
       <c r="R17" t="n">
-        <v>6837047</v>
+        <v>6836895</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118614078</v>
+        <v>118614095</v>
       </c>
       <c r="B18" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,21 +2336,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455889</v>
+        <v>455985</v>
       </c>
       <c r="R18" t="n">
-        <v>6836903</v>
+        <v>6836979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118614091</v>
+        <v>118614108</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455881</v>
+        <v>455960</v>
       </c>
       <c r="R19" t="n">
-        <v>6836923</v>
+        <v>6837047</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118614079</v>
+        <v>118614093</v>
       </c>
       <c r="B20" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,21 +2540,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455886</v>
+        <v>456008</v>
       </c>
       <c r="R20" t="n">
-        <v>6836900</v>
+        <v>6837047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118614082</v>
+        <v>118614088</v>
       </c>
       <c r="B21" t="n">
-        <v>79102</v>
+        <v>57443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455942</v>
+        <v>455935</v>
       </c>
       <c r="R21" t="n">
-        <v>6837052</v>
+        <v>6836858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118614093</v>
+        <v>118614079</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
+        <v>79109</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456008</v>
+        <v>455886</v>
       </c>
       <c r="R22" t="n">
-        <v>6837047</v>
+        <v>6836900</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118614104</v>
+        <v>118614100</v>
       </c>
       <c r="B23" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455867</v>
+        <v>455939</v>
       </c>
       <c r="R23" t="n">
-        <v>6836907</v>
+        <v>6836859</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118614110</v>
+        <v>118614102</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456021</v>
+        <v>455889</v>
       </c>
       <c r="R24" t="n">
-        <v>6836968</v>
+        <v>6836903</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118614106</v>
+        <v>118614109</v>
       </c>
       <c r="B25" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455886</v>
+        <v>456008</v>
       </c>
       <c r="R25" t="n">
-        <v>6836975</v>
+        <v>6837047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118614086</v>
+        <v>118614087</v>
       </c>
       <c r="B26" t="n">
-        <v>78583</v>
+        <v>78590</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455907</v>
+        <v>455959</v>
       </c>
       <c r="R26" t="n">
-        <v>6837012</v>
+        <v>6837052</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118614083</v>
+        <v>118614078</v>
       </c>
       <c r="B27" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455947</v>
+        <v>455889</v>
       </c>
       <c r="R27" t="n">
-        <v>6837045</v>
+        <v>6836903</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118614105</v>
+        <v>118614111</v>
       </c>
       <c r="B28" t="n">
-        <v>78220</v>
+        <v>78136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455881</v>
+        <v>455971</v>
       </c>
       <c r="R28" t="n">
-        <v>6836923</v>
+        <v>6837047</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118614098</v>
+        <v>118614104</v>
       </c>
       <c r="B29" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455984</v>
+        <v>455867</v>
       </c>
       <c r="R29" t="n">
-        <v>6836875</v>
+        <v>6836907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118614107</v>
+        <v>118614098</v>
       </c>
       <c r="B30" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455942</v>
+        <v>455984</v>
       </c>
       <c r="R30" t="n">
-        <v>6836999</v>
+        <v>6836875</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118614109</v>
+        <v>118614086</v>
       </c>
       <c r="B31" t="n">
-        <v>78220</v>
+        <v>78590</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456008</v>
+        <v>455907</v>
       </c>
       <c r="R31" t="n">
-        <v>6837047</v>
+        <v>6837012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118614100</v>
+        <v>118614082</v>
       </c>
       <c r="B32" t="n">
-        <v>78220</v>
+        <v>79109</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455939</v>
+        <v>455942</v>
       </c>
       <c r="R32" t="n">
-        <v>6836859</v>
+        <v>6837052</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118614103</v>
+        <v>118614090</v>
       </c>
       <c r="B33" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455886</v>
+        <v>455935</v>
       </c>
       <c r="R33" t="n">
-        <v>6836900</v>
+        <v>6836857</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118614090</v>
+        <v>118614105</v>
       </c>
       <c r="B34" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455935</v>
+        <v>455881</v>
       </c>
       <c r="R34" t="n">
-        <v>6836857</v>
+        <v>6836923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118727521</v>
+        <v>118727600</v>
       </c>
       <c r="B35" t="n">
-        <v>79102</v>
+        <v>80448</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4070,35 +4070,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455919</v>
+        <v>455702</v>
       </c>
       <c r="R35" t="n">
-        <v>6836937</v>
+        <v>6837084</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4157,10 +4156,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118727537</v>
+        <v>118727622</v>
       </c>
       <c r="B36" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4173,35 +4172,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456027</v>
+        <v>455747</v>
       </c>
       <c r="R36" t="n">
-        <v>6836806</v>
+        <v>6837101</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4258,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118727662</v>
+        <v>118727640</v>
       </c>
       <c r="B37" t="n">
-        <v>77416</v>
+        <v>78491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4276,21 +4274,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4300,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455700</v>
+        <v>455987</v>
       </c>
       <c r="R37" t="n">
-        <v>6837084</v>
+        <v>6836765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4360,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118727544</v>
+        <v>118727582</v>
       </c>
       <c r="B38" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,35 +4376,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456065</v>
+        <v>455915</v>
       </c>
       <c r="R38" t="n">
-        <v>6836867</v>
+        <v>6836954</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4439,6 +4444,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118727617</v>
+        <v>118727523</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4481,34 +4491,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455720</v>
+        <v>455933</v>
       </c>
       <c r="R39" t="n">
-        <v>6837077</v>
+        <v>6836859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727596</v>
+        <v>118727612</v>
       </c>
       <c r="B40" t="n">
-        <v>78221</v>
+        <v>90661</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4579,25 +4590,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4607,10 +4618,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455956</v>
+        <v>455930</v>
       </c>
       <c r="R40" t="n">
-        <v>6837009</v>
+        <v>6836843</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,10 +4680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727588</v>
+        <v>118727624</v>
       </c>
       <c r="B41" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,21 +4696,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4709,10 +4720,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455938</v>
+        <v>455844</v>
       </c>
       <c r="R41" t="n">
-        <v>6836861</v>
+        <v>6837118</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,10 +4782,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727556</v>
+        <v>118727581</v>
       </c>
       <c r="B42" t="n">
-        <v>79073</v>
+        <v>57290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,35 +4798,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456028</v>
+        <v>455926</v>
       </c>
       <c r="R42" t="n">
-        <v>6836813</v>
+        <v>6836949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4848,6 +4866,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4874,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727554</v>
+        <v>118727550</v>
       </c>
       <c r="B43" t="n">
-        <v>79073</v>
+        <v>79080</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4915,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456036</v>
+        <v>455970</v>
       </c>
       <c r="R43" t="n">
-        <v>6836795</v>
+        <v>6836763</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4977,10 +5000,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727612</v>
+        <v>118727543</v>
       </c>
       <c r="B44" t="n">
-        <v>90654</v>
+        <v>79109</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4989,38 +5012,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455930</v>
+        <v>456050</v>
       </c>
       <c r="R44" t="n">
-        <v>6836843</v>
+        <v>6836858</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727546</v>
+        <v>118727606</v>
       </c>
       <c r="B45" t="n">
-        <v>79073</v>
+        <v>78227</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5095,35 +5119,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455932</v>
+        <v>456025</v>
       </c>
       <c r="R45" t="n">
-        <v>6836858</v>
+        <v>6836801</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,10 +5205,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727629</v>
+        <v>118727623</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5222,10 +5245,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455870</v>
+        <v>455802</v>
       </c>
       <c r="R46" t="n">
-        <v>6837153</v>
+        <v>6837089</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5284,10 +5307,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727587</v>
+        <v>118727537</v>
       </c>
       <c r="B47" t="n">
-        <v>78221</v>
+        <v>79109</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5300,34 +5323,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455933</v>
+        <v>456027</v>
       </c>
       <c r="R47" t="n">
-        <v>6836859</v>
+        <v>6836806</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,10 +5410,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118727526</v>
+        <v>118727658</v>
       </c>
       <c r="B48" t="n">
-        <v>79102</v>
+        <v>78136</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5402,35 +5426,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455943</v>
+        <v>455957</v>
       </c>
       <c r="R48" t="n">
-        <v>6836795</v>
+        <v>6836744</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5512,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118727543</v>
+        <v>118727545</v>
       </c>
       <c r="B49" t="n">
-        <v>79102</v>
+        <v>79080</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5528,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5553,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456050</v>
+        <v>455700</v>
       </c>
       <c r="R49" t="n">
-        <v>6836858</v>
+        <v>6837083</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5592,10 +5615,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118727604</v>
+        <v>118727590</v>
       </c>
       <c r="B50" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5608,21 +5631,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5632,10 +5655,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455931</v>
+        <v>455955</v>
       </c>
       <c r="R50" t="n">
-        <v>6836858</v>
+        <v>6836833</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5694,10 +5717,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118727531</v>
+        <v>118727549</v>
       </c>
       <c r="B51" t="n">
-        <v>79102</v>
+        <v>79080</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5710,21 +5733,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5735,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455918</v>
+        <v>455956</v>
       </c>
       <c r="R51" t="n">
-        <v>6836750</v>
+        <v>6836745</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118727507</v>
+        <v>118727586</v>
       </c>
       <c r="B52" t="n">
-        <v>78518</v>
+        <v>78228</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5813,35 +5836,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455726</v>
+        <v>455865</v>
       </c>
       <c r="R52" t="n">
-        <v>6837099</v>
+        <v>6836943</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5900,10 +5922,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118727560</v>
+        <v>118727588</v>
       </c>
       <c r="B53" t="n">
-        <v>78583</v>
+        <v>78228</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5916,45 +5938,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455904</v>
+        <v>455938</v>
       </c>
       <c r="R53" t="n">
-        <v>6836777</v>
+        <v>6836861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,7 +6006,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6014,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118727511</v>
+        <v>118727562</v>
       </c>
       <c r="B54" t="n">
-        <v>78518</v>
+        <v>78590</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6030,35 +6040,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455951</v>
+        <v>455956</v>
       </c>
       <c r="R54" t="n">
-        <v>6836741</v>
+        <v>6836833</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6117,10 +6126,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118727513</v>
+        <v>118727560</v>
       </c>
       <c r="B55" t="n">
-        <v>78518</v>
+        <v>78590</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6133,35 +6142,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455971</v>
+        <v>455904</v>
       </c>
       <c r="R55" t="n">
-        <v>6836747</v>
+        <v>6836777</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6202,6 +6221,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6220,10 +6240,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118727503</v>
+        <v>118727620</v>
       </c>
       <c r="B56" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6236,21 +6256,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6260,10 +6280,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456028</v>
+        <v>455733</v>
       </c>
       <c r="R56" t="n">
-        <v>6836799</v>
+        <v>6837103</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6322,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118727527</v>
+        <v>118727520</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6363,10 +6383,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455903</v>
+        <v>455867</v>
       </c>
       <c r="R57" t="n">
-        <v>6836778</v>
+        <v>6836942</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6425,10 +6445,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118727593</v>
+        <v>118727533</v>
       </c>
       <c r="B58" t="n">
-        <v>78221</v>
+        <v>79109</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6441,34 +6461,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456027</v>
+        <v>455956</v>
       </c>
       <c r="R58" t="n">
-        <v>6836806</v>
+        <v>6836745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6527,10 +6548,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118727609</v>
+        <v>118727592</v>
       </c>
       <c r="B59" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6543,21 +6564,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6567,10 +6588,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456053</v>
+        <v>456025</v>
       </c>
       <c r="R59" t="n">
-        <v>6836858</v>
+        <v>6836800</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6629,10 +6650,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118727640</v>
+        <v>118727611</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
+        <v>90661</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6641,25 +6662,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6669,10 +6690,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455987</v>
+        <v>455716</v>
       </c>
       <c r="R60" t="n">
-        <v>6836765</v>
+        <v>6837046</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6731,10 +6752,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118727633</v>
+        <v>118727665</v>
       </c>
       <c r="B61" t="n">
-        <v>78484</v>
+        <v>77875</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6747,21 +6768,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6771,10 +6792,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455917</v>
+        <v>455701</v>
       </c>
       <c r="R61" t="n">
-        <v>6836957</v>
+        <v>6837084</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6833,10 +6854,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118727549</v>
+        <v>118727541</v>
       </c>
       <c r="B62" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6849,21 +6870,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6874,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455956</v>
+        <v>456048</v>
       </c>
       <c r="R62" t="n">
-        <v>6836745</v>
+        <v>6836813</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6936,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118727598</v>
+        <v>118727527</v>
       </c>
       <c r="B63" t="n">
-        <v>78221</v>
+        <v>79109</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6952,34 +6973,35 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455878</v>
+        <v>455903</v>
       </c>
       <c r="R63" t="n">
-        <v>6836925</v>
+        <v>6836778</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7038,10 +7060,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118727651</v>
+        <v>118727619</v>
       </c>
       <c r="B64" t="n">
-        <v>90749</v>
+        <v>78491</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7050,25 +7072,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7078,10 +7100,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455972</v>
+        <v>455726</v>
       </c>
       <c r="R64" t="n">
-        <v>6836775</v>
+        <v>6837099</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7140,10 +7162,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727600</v>
+        <v>118727635</v>
       </c>
       <c r="B65" t="n">
-        <v>80441</v>
+        <v>78491</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7156,21 +7178,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7180,10 +7202,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455702</v>
+        <v>455915</v>
       </c>
       <c r="R65" t="n">
-        <v>6837084</v>
+        <v>6836927</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7242,10 +7264,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118727603</v>
+        <v>118727542</v>
       </c>
       <c r="B66" t="n">
-        <v>80441</v>
+        <v>79109</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7258,34 +7280,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456024</v>
+        <v>456022</v>
       </c>
       <c r="R66" t="n">
-        <v>6836818</v>
+        <v>6836819</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7344,10 +7367,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118727525</v>
+        <v>118727524</v>
       </c>
       <c r="B67" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7385,10 +7408,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455924</v>
+        <v>455955</v>
       </c>
       <c r="R67" t="n">
-        <v>6836801</v>
+        <v>6836833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7447,10 +7470,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118727648</v>
+        <v>118727539</v>
       </c>
       <c r="B68" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7463,34 +7486,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456055</v>
+        <v>456035</v>
       </c>
       <c r="R68" t="n">
-        <v>6836875</v>
+        <v>6836794</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,10 +7573,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727630</v>
+        <v>118727553</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7565,34 +7589,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455860</v>
+        <v>456026</v>
       </c>
       <c r="R69" t="n">
-        <v>6837129</v>
+        <v>6836798</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7651,10 +7676,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727639</v>
+        <v>118727660</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>78136</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7667,21 +7692,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7691,10 +7716,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455967</v>
+        <v>456065</v>
       </c>
       <c r="R70" t="n">
-        <v>6836746</v>
+        <v>6836867</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,10 +7778,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727618</v>
+        <v>118727607</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7769,21 +7794,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7793,10 +7818,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455724</v>
+        <v>456027</v>
       </c>
       <c r="R71" t="n">
-        <v>6837080</v>
+        <v>6836806</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7855,10 +7880,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727519</v>
+        <v>118727587</v>
       </c>
       <c r="B72" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7871,35 +7896,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455850</v>
+        <v>455933</v>
       </c>
       <c r="R72" t="n">
-        <v>6837094</v>
+        <v>6836859</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7958,10 +7982,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727529</v>
+        <v>118727558</v>
       </c>
       <c r="B73" t="n">
-        <v>79102</v>
+        <v>78590</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7974,35 +7998,45 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455885</v>
+        <v>456036</v>
       </c>
       <c r="R73" t="n">
-        <v>6836757</v>
+        <v>6836794</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8043,6 +8077,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8061,10 +8096,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118727627</v>
+        <v>118727653</v>
       </c>
       <c r="B74" t="n">
-        <v>78484</v>
+        <v>94520</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8073,25 +8108,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8101,10 +8136,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455891</v>
+        <v>456022</v>
       </c>
       <c r="R74" t="n">
-        <v>6836950</v>
+        <v>6836970</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8163,10 +8198,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118727637</v>
+        <v>118727608</v>
       </c>
       <c r="B75" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8179,21 +8214,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8203,10 +8238,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455922</v>
+        <v>456041</v>
       </c>
       <c r="R75" t="n">
-        <v>6836913</v>
+        <v>6836795</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8265,10 +8300,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118727632</v>
+        <v>118727591</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8281,21 +8316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8305,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455916</v>
+        <v>455924</v>
       </c>
       <c r="R76" t="n">
-        <v>6836963</v>
+        <v>6836800</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8367,10 +8402,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118727583</v>
+        <v>118727556</v>
       </c>
       <c r="B77" t="n">
-        <v>78221</v>
+        <v>79080</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8383,34 +8418,35 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456050</v>
+        <v>456028</v>
       </c>
       <c r="R77" t="n">
-        <v>6836858</v>
+        <v>6836813</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8469,10 +8505,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118727595</v>
+        <v>118727598</v>
       </c>
       <c r="B78" t="n">
-        <v>78221</v>
+        <v>78228</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8509,10 +8545,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455986</v>
+        <v>455878</v>
       </c>
       <c r="R78" t="n">
-        <v>6836980</v>
+        <v>6836925</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8571,10 +8607,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118727591</v>
+        <v>118727548</v>
       </c>
       <c r="B79" t="n">
-        <v>78221</v>
+        <v>79080</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8587,34 +8623,35 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455924</v>
+        <v>455926</v>
       </c>
       <c r="R79" t="n">
-        <v>6836800</v>
+        <v>6836752</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8673,10 +8710,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118727610</v>
+        <v>118727554</v>
       </c>
       <c r="B80" t="n">
-        <v>78220</v>
+        <v>79080</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8689,34 +8726,35 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455955</v>
+        <v>456036</v>
       </c>
       <c r="R80" t="n">
-        <v>6837009</v>
+        <v>6836795</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8775,10 +8813,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118727528</v>
+        <v>118727585</v>
       </c>
       <c r="B81" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8791,35 +8829,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455898</v>
+        <v>455930</v>
       </c>
       <c r="R81" t="n">
-        <v>6836767</v>
+        <v>6836897</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8878,10 +8915,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118727582</v>
+        <v>118727596</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>78228</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8894,42 +8931,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>455915</v>
+        <v>455956</v>
       </c>
       <c r="R82" t="n">
-        <v>6836954</v>
+        <v>6837009</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8962,11 +8991,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8993,10 +9017,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118727517</v>
+        <v>118727599</v>
       </c>
       <c r="B83" t="n">
-        <v>79102</v>
+        <v>90973</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9009,35 +9033,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>5467</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>455986</v>
+        <v>455957</v>
       </c>
       <c r="R83" t="n">
-        <v>6836980</v>
+        <v>6836745</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9096,10 +9119,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118727562</v>
+        <v>118727503</v>
       </c>
       <c r="B84" t="n">
-        <v>78583</v>
+        <v>78525</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9112,21 +9135,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9136,10 +9159,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>455956</v>
+        <v>456028</v>
       </c>
       <c r="R84" t="n">
-        <v>6836833</v>
+        <v>6836799</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9198,10 +9221,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118727558</v>
+        <v>118727629</v>
       </c>
       <c r="B85" t="n">
-        <v>78583</v>
+        <v>78491</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9214,45 +9237,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>456036</v>
+        <v>455870</v>
       </c>
       <c r="R85" t="n">
-        <v>6836794</v>
+        <v>6837153</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9293,7 +9305,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9312,10 +9323,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118727664</v>
+        <v>118727529</v>
       </c>
       <c r="B86" t="n">
-        <v>77416</v>
+        <v>79109</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9328,34 +9339,35 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>456028</v>
+        <v>455885</v>
       </c>
       <c r="R86" t="n">
-        <v>6836814</v>
+        <v>6836757</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9414,10 +9426,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727532</v>
+        <v>118727521</v>
       </c>
       <c r="B87" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9455,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>455926</v>
+        <v>455919</v>
       </c>
       <c r="R87" t="n">
-        <v>6836752</v>
+        <v>6836937</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9517,10 +9529,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727530</v>
+        <v>118727637</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,35 +9545,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455892</v>
+        <v>455922</v>
       </c>
       <c r="R88" t="n">
-        <v>6836753</v>
+        <v>6836913</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9620,10 +9631,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118727636</v>
+        <v>118727557</v>
       </c>
       <c r="B89" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9636,34 +9647,35 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455925</v>
+        <v>456053</v>
       </c>
       <c r="R89" t="n">
-        <v>6836919</v>
+        <v>6836858</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9722,10 +9734,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118727592</v>
+        <v>118727547</v>
       </c>
       <c r="B90" t="n">
-        <v>78221</v>
+        <v>79080</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9738,34 +9750,35 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>456025</v>
+        <v>455904</v>
       </c>
       <c r="R90" t="n">
-        <v>6836800</v>
+        <v>6836778</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9824,10 +9837,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118727631</v>
+        <v>118727526</v>
       </c>
       <c r="B91" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9840,34 +9853,35 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>455914</v>
+        <v>455943</v>
       </c>
       <c r="R91" t="n">
-        <v>6836965</v>
+        <v>6836795</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9926,10 +9940,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118727545</v>
+        <v>118727530</v>
       </c>
       <c r="B92" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9942,21 +9956,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9967,10 +9981,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>455700</v>
+        <v>455892</v>
       </c>
       <c r="R92" t="n">
-        <v>6837083</v>
+        <v>6836753</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10029,10 +10043,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118727590</v>
+        <v>118727510</v>
       </c>
       <c r="B93" t="n">
-        <v>78221</v>
+        <v>78525</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10045,34 +10059,35 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>455955</v>
+        <v>455912</v>
       </c>
       <c r="R93" t="n">
-        <v>6836833</v>
+        <v>6836969</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10131,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118727502</v>
+        <v>118727508</v>
       </c>
       <c r="B94" t="n">
-        <v>78518</v>
+        <v>78525</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,16 +10180,17 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>456023</v>
+        <v>455765</v>
       </c>
       <c r="R94" t="n">
-        <v>6836783</v>
+        <v>6837108</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10233,10 +10249,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118727508</v>
+        <v>118727601</v>
       </c>
       <c r="B95" t="n">
-        <v>78518</v>
+        <v>80448</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10249,35 +10265,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455765</v>
+        <v>455913</v>
       </c>
       <c r="R95" t="n">
-        <v>6837108</v>
+        <v>6836820</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10336,10 +10351,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118727667</v>
+        <v>118727532</v>
       </c>
       <c r="B96" t="n">
-        <v>77868</v>
+        <v>79109</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10352,34 +10367,35 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>456035</v>
+        <v>455926</v>
       </c>
       <c r="R96" t="n">
-        <v>6836796</v>
+        <v>6836752</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10438,10 +10454,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118727506</v>
+        <v>118727518</v>
       </c>
       <c r="B97" t="n">
-        <v>78518</v>
+        <v>79109</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10454,21 +10470,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10479,10 +10495,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455726</v>
+        <v>455952</v>
       </c>
       <c r="R97" t="n">
-        <v>6837083</v>
+        <v>6836992</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10541,10 +10557,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118727611</v>
+        <v>118727544</v>
       </c>
       <c r="B98" t="n">
-        <v>90654</v>
+        <v>79109</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10553,38 +10569,39 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455716</v>
+        <v>456065</v>
       </c>
       <c r="R98" t="n">
-        <v>6837046</v>
+        <v>6836867</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10646,7 +10663,7 @@
         <v>118727579</v>
       </c>
       <c r="B99" t="n">
-        <v>78573</v>
+        <v>78580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10745,10 +10762,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118727542</v>
+        <v>118727630</v>
       </c>
       <c r="B100" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10761,35 +10778,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>456022</v>
+        <v>455860</v>
       </c>
       <c r="R100" t="n">
-        <v>6836819</v>
+        <v>6837129</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10848,10 +10864,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118727538</v>
+        <v>118727617</v>
       </c>
       <c r="B101" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10864,35 +10880,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>456041</v>
+        <v>455720</v>
       </c>
       <c r="R101" t="n">
-        <v>6836794</v>
+        <v>6837077</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10951,10 +10966,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118727626</v>
+        <v>118727511</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10967,34 +10982,35 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455897</v>
+        <v>455951</v>
       </c>
       <c r="R102" t="n">
-        <v>6836935</v>
+        <v>6836741</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11053,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118727619</v>
+        <v>118727502</v>
       </c>
       <c r="B103" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11069,21 +11085,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11093,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>455726</v>
+        <v>456023</v>
       </c>
       <c r="R103" t="n">
-        <v>6837099</v>
+        <v>6836783</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11155,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118727608</v>
+        <v>118727604</v>
       </c>
       <c r="B104" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11195,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>456041</v>
+        <v>455931</v>
       </c>
       <c r="R104" t="n">
-        <v>6836795</v>
+        <v>6836858</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11257,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118727606</v>
+        <v>118727632</v>
       </c>
       <c r="B105" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11273,21 +11289,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11297,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>456025</v>
+        <v>455916</v>
       </c>
       <c r="R105" t="n">
-        <v>6836801</v>
+        <v>6836963</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11359,10 +11375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118727565</v>
+        <v>118727655</v>
       </c>
       <c r="B106" t="n">
-        <v>57443</v>
+        <v>78136</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11375,21 +11391,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11399,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455864</v>
+        <v>455973</v>
       </c>
       <c r="R106" t="n">
-        <v>6837158</v>
+        <v>6836775</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11461,10 +11477,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118727653</v>
+        <v>118727652</v>
       </c>
       <c r="B107" t="n">
-        <v>94513</v>
+        <v>94520</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11501,10 +11517,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>456022</v>
+        <v>455841</v>
       </c>
       <c r="R107" t="n">
-        <v>6836970</v>
+        <v>6837101</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11563,10 +11579,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118727586</v>
+        <v>118727625</v>
       </c>
       <c r="B108" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11579,21 +11595,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11603,10 +11619,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>455865</v>
+        <v>455868</v>
       </c>
       <c r="R108" t="n">
-        <v>6836943</v>
+        <v>6837146</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11665,10 +11681,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118727597</v>
+        <v>118727610</v>
       </c>
       <c r="B109" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11681,21 +11697,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11705,10 +11721,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>455943</v>
+        <v>455955</v>
       </c>
       <c r="R109" t="n">
-        <v>6836998</v>
+        <v>6837009</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11767,10 +11783,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727594</v>
+        <v>118727618</v>
       </c>
       <c r="B110" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11783,21 +11799,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11807,10 +11823,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>456008</v>
+        <v>455724</v>
       </c>
       <c r="R110" t="n">
-        <v>6836969</v>
+        <v>6837080</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11869,10 +11885,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727658</v>
+        <v>118727667</v>
       </c>
       <c r="B111" t="n">
-        <v>78129</v>
+        <v>77875</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11885,21 +11901,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11909,10 +11925,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455957</v>
+        <v>456035</v>
       </c>
       <c r="R111" t="n">
-        <v>6836744</v>
+        <v>6836796</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11971,10 +11987,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727539</v>
+        <v>118727636</v>
       </c>
       <c r="B112" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11987,35 +12003,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>456035</v>
+        <v>455925</v>
       </c>
       <c r="R112" t="n">
-        <v>6836794</v>
+        <v>6836919</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12074,10 +12089,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727625</v>
+        <v>118727603</v>
       </c>
       <c r="B113" t="n">
-        <v>78484</v>
+        <v>80448</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12090,21 +12105,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12114,10 +12129,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455868</v>
+        <v>456024</v>
       </c>
       <c r="R113" t="n">
-        <v>6837146</v>
+        <v>6836818</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12176,10 +12191,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727635</v>
+        <v>118727595</v>
       </c>
       <c r="B114" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12192,21 +12207,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12216,10 +12231,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455915</v>
+        <v>455986</v>
       </c>
       <c r="R114" t="n">
-        <v>6836927</v>
+        <v>6836980</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12278,10 +12293,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727599</v>
+        <v>118727664</v>
       </c>
       <c r="B115" t="n">
-        <v>90966</v>
+        <v>77423</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12294,21 +12309,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5467</v>
+        <v>6487</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12318,10 +12333,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455957</v>
+        <v>456028</v>
       </c>
       <c r="R115" t="n">
-        <v>6836745</v>
+        <v>6836814</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12380,10 +12395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727620</v>
+        <v>118727651</v>
       </c>
       <c r="B116" t="n">
-        <v>78484</v>
+        <v>90756</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12392,25 +12407,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12420,10 +12435,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455733</v>
+        <v>455972</v>
       </c>
       <c r="R116" t="n">
-        <v>6837103</v>
+        <v>6836775</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12482,10 +12497,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727547</v>
+        <v>118727594</v>
       </c>
       <c r="B117" t="n">
-        <v>79073</v>
+        <v>78228</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12498,35 +12513,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455904</v>
+        <v>456008</v>
       </c>
       <c r="R117" t="n">
-        <v>6836778</v>
+        <v>6836969</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12585,10 +12599,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727585</v>
+        <v>118727626</v>
       </c>
       <c r="B118" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12601,21 +12615,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12625,10 +12639,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455930</v>
+        <v>455897</v>
       </c>
       <c r="R118" t="n">
-        <v>6836897</v>
+        <v>6836935</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12687,10 +12701,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727581</v>
+        <v>118727639</v>
       </c>
       <c r="B119" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12703,42 +12717,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455926</v>
+        <v>455967</v>
       </c>
       <c r="R119" t="n">
-        <v>6836949</v>
+        <v>6836746</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12771,11 +12777,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12802,10 +12803,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727601</v>
+        <v>118727506</v>
       </c>
       <c r="B120" t="n">
-        <v>80441</v>
+        <v>78525</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12818,34 +12819,35 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455913</v>
+        <v>455726</v>
       </c>
       <c r="R120" t="n">
-        <v>6836820</v>
+        <v>6837083</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,10 +12906,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118727523</v>
+        <v>118727513</v>
       </c>
       <c r="B121" t="n">
-        <v>79102</v>
+        <v>78525</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12920,21 +12922,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12945,10 +12947,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455933</v>
+        <v>455971</v>
       </c>
       <c r="R121" t="n">
-        <v>6836859</v>
+        <v>6836747</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13007,10 +13009,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118727624</v>
+        <v>118727593</v>
       </c>
       <c r="B122" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13023,21 +13025,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13047,10 +13049,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455844</v>
+        <v>456027</v>
       </c>
       <c r="R122" t="n">
-        <v>6837118</v>
+        <v>6836806</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13109,10 +13111,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118727510</v>
+        <v>118727633</v>
       </c>
       <c r="B123" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13125,35 +13127,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>455912</v>
+        <v>455917</v>
       </c>
       <c r="R123" t="n">
-        <v>6836969</v>
+        <v>6836957</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13212,10 +13213,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118727652</v>
+        <v>118727528</v>
       </c>
       <c r="B124" t="n">
-        <v>94513</v>
+        <v>79109</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13224,38 +13225,39 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>455841</v>
+        <v>455898</v>
       </c>
       <c r="R124" t="n">
-        <v>6837101</v>
+        <v>6836767</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13314,10 +13316,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118727541</v>
+        <v>118727583</v>
       </c>
       <c r="B125" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,35 +13332,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>456048</v>
+        <v>456050</v>
       </c>
       <c r="R125" t="n">
-        <v>6836813</v>
+        <v>6836858</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13417,10 +13418,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118727524</v>
+        <v>118727609</v>
       </c>
       <c r="B126" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13433,35 +13434,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455955</v>
+        <v>456053</v>
       </c>
       <c r="R126" t="n">
-        <v>6836833</v>
+        <v>6836858</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13520,10 +13520,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118727533</v>
+        <v>118727519</v>
       </c>
       <c r="B127" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13561,10 +13561,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455956</v>
+        <v>455850</v>
       </c>
       <c r="R127" t="n">
-        <v>6836745</v>
+        <v>6837094</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13626,7 +13626,7 @@
         <v>118727668</v>
       </c>
       <c r="B128" t="n">
-        <v>77868</v>
+        <v>77875</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118727557</v>
+        <v>118727561</v>
       </c>
       <c r="B129" t="n">
-        <v>79073</v>
+        <v>78590</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13741,35 +13741,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>456053</v>
+        <v>455930</v>
       </c>
       <c r="R129" t="n">
-        <v>6836858</v>
+        <v>6836890</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13828,10 +13827,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118727561</v>
+        <v>118727631</v>
       </c>
       <c r="B130" t="n">
-        <v>78583</v>
+        <v>78491</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,21 +13843,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13867,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455930</v>
+        <v>455914</v>
       </c>
       <c r="R130" t="n">
-        <v>6836890</v>
+        <v>6836965</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13930,10 +13929,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118727520</v>
+        <v>118727662</v>
       </c>
       <c r="B131" t="n">
-        <v>79102</v>
+        <v>77423</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13946,35 +13945,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455867</v>
+        <v>455700</v>
       </c>
       <c r="R131" t="n">
-        <v>6836942</v>
+        <v>6837084</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14033,10 +14031,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118727665</v>
+        <v>118727638</v>
       </c>
       <c r="B132" t="n">
-        <v>77868</v>
+        <v>78491</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14049,21 +14047,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14073,10 +14071,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455701</v>
+        <v>455933</v>
       </c>
       <c r="R132" t="n">
-        <v>6837084</v>
+        <v>6836917</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14135,10 +14133,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118727638</v>
+        <v>118727531</v>
       </c>
       <c r="B133" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14151,34 +14149,35 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455933</v>
+        <v>455918</v>
       </c>
       <c r="R133" t="n">
-        <v>6836917</v>
+        <v>6836750</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14237,10 +14236,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118727607</v>
+        <v>118727584</v>
       </c>
       <c r="B134" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14253,21 +14252,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14276,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456027</v>
+        <v>456053</v>
       </c>
       <c r="R134" t="n">
-        <v>6836806</v>
+        <v>6836858</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14339,10 +14338,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118727623</v>
+        <v>118727627</v>
       </c>
       <c r="B135" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14379,10 +14378,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455802</v>
+        <v>455891</v>
       </c>
       <c r="R135" t="n">
-        <v>6837089</v>
+        <v>6836950</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14441,10 +14440,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118727548</v>
+        <v>118727525</v>
       </c>
       <c r="B136" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,21 +14456,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14482,10 +14481,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455926</v>
+        <v>455924</v>
       </c>
       <c r="R136" t="n">
-        <v>6836752</v>
+        <v>6836801</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14544,10 +14543,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118727584</v>
+        <v>118727507</v>
       </c>
       <c r="B137" t="n">
-        <v>78221</v>
+        <v>78525</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14560,34 +14559,35 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>456053</v>
+        <v>455726</v>
       </c>
       <c r="R137" t="n">
-        <v>6836858</v>
+        <v>6837099</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14646,10 +14646,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118727550</v>
+        <v>118727565</v>
       </c>
       <c r="B138" t="n">
-        <v>79073</v>
+        <v>57443</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14662,35 +14662,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455970</v>
+        <v>455864</v>
       </c>
       <c r="R138" t="n">
-        <v>6836763</v>
+        <v>6837158</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14749,10 +14748,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118727553</v>
+        <v>118727517</v>
       </c>
       <c r="B139" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14765,21 +14764,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14790,10 +14789,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>456026</v>
+        <v>455986</v>
       </c>
       <c r="R139" t="n">
-        <v>6836798</v>
+        <v>6836980</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14852,10 +14851,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118727622</v>
+        <v>118727648</v>
       </c>
       <c r="B140" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14892,10 +14891,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455747</v>
+        <v>456055</v>
       </c>
       <c r="R140" t="n">
-        <v>6837101</v>
+        <v>6836875</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14954,10 +14953,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118727655</v>
+        <v>118727538</v>
       </c>
       <c r="B141" t="n">
-        <v>78129</v>
+        <v>79109</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14970,34 +14969,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455973</v>
+        <v>456041</v>
       </c>
       <c r="R141" t="n">
-        <v>6836775</v>
+        <v>6836794</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15056,10 +15056,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118727660</v>
+        <v>118727546</v>
       </c>
       <c r="B142" t="n">
-        <v>78129</v>
+        <v>79080</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15072,34 +15072,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>456065</v>
+        <v>455932</v>
       </c>
       <c r="R142" t="n">
-        <v>6836867</v>
+        <v>6836858</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15158,10 +15159,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118727518</v>
+        <v>118727597</v>
       </c>
       <c r="B143" t="n">
-        <v>79102</v>
+        <v>78228</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15174,35 +15175,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455952</v>
+        <v>455943</v>
       </c>
       <c r="R143" t="n">
-        <v>6836992</v>
+        <v>6836998</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118614106</v>
+        <v>118614091</v>
       </c>
       <c r="B5" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455886</v>
+        <v>455881</v>
       </c>
       <c r="R5" t="n">
-        <v>6836975</v>
+        <v>6836923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614091</v>
+        <v>118614076</v>
       </c>
       <c r="B6" t="n">
-        <v>78228</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455881</v>
+        <v>456018</v>
       </c>
       <c r="R6" t="n">
-        <v>6836923</v>
+        <v>6837020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614076</v>
+        <v>118614106</v>
       </c>
       <c r="B7" t="n">
-        <v>78525</v>
+        <v>78227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456018</v>
+        <v>455886</v>
       </c>
       <c r="R7" t="n">
-        <v>6837020</v>
+        <v>6836975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -6548,10 +6548,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118727592</v>
+        <v>118727665</v>
       </c>
       <c r="B59" t="n">
-        <v>78228</v>
+        <v>77875</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6564,21 +6564,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456025</v>
+        <v>455701</v>
       </c>
       <c r="R59" t="n">
-        <v>6836800</v>
+        <v>6837084</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6650,10 +6650,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118727611</v>
+        <v>118727541</v>
       </c>
       <c r="B60" t="n">
-        <v>90661</v>
+        <v>79109</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,38 +6662,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455716</v>
+        <v>456048</v>
       </c>
       <c r="R60" t="n">
-        <v>6837046</v>
+        <v>6836813</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6752,10 +6753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118727665</v>
+        <v>118727611</v>
       </c>
       <c r="B61" t="n">
-        <v>77875</v>
+        <v>90661</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,25 +6765,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6792,10 +6793,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455701</v>
+        <v>455716</v>
       </c>
       <c r="R61" t="n">
-        <v>6837084</v>
+        <v>6837046</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6854,10 +6855,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118727541</v>
+        <v>118727592</v>
       </c>
       <c r="B62" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6870,35 +6871,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456048</v>
+        <v>456025</v>
       </c>
       <c r="R62" t="n">
-        <v>6836813</v>
+        <v>6836800</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -14851,10 +14851,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118727648</v>
+        <v>118727546</v>
       </c>
       <c r="B140" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14867,34 +14867,35 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>456055</v>
+        <v>455932</v>
       </c>
       <c r="R140" t="n">
-        <v>6836875</v>
+        <v>6836858</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14953,10 +14954,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118727538</v>
+        <v>118727597</v>
       </c>
       <c r="B141" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14969,35 +14970,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>456041</v>
+        <v>455943</v>
       </c>
       <c r="R141" t="n">
-        <v>6836794</v>
+        <v>6836998</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15056,10 +15056,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118727546</v>
+        <v>118727648</v>
       </c>
       <c r="B142" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15072,35 +15072,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455932</v>
+        <v>456055</v>
       </c>
       <c r="R142" t="n">
-        <v>6836858</v>
+        <v>6836875</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15159,10 +15158,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118727597</v>
+        <v>118727538</v>
       </c>
       <c r="B143" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15175,34 +15174,35 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455943</v>
+        <v>456041</v>
       </c>
       <c r="R143" t="n">
-        <v>6836998</v>
+        <v>6836794</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118614101</v>
+        <v>118614079</v>
       </c>
       <c r="B2" t="n">
-        <v>78227</v>
+        <v>79109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455923</v>
+        <v>455886</v>
       </c>
       <c r="R2" t="n">
-        <v>6836875</v>
+        <v>6836900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118614107</v>
+        <v>118614097</v>
       </c>
       <c r="B3" t="n">
         <v>78227</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455942</v>
+        <v>456025</v>
       </c>
       <c r="R3" t="n">
-        <v>6836999</v>
+        <v>6836910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118614096</v>
+        <v>118614103</v>
       </c>
       <c r="B4" t="n">
         <v>78227</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456010</v>
+        <v>455886</v>
       </c>
       <c r="R4" t="n">
-        <v>6836965</v>
+        <v>6836900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118614091</v>
+        <v>118614100</v>
       </c>
       <c r="B5" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455881</v>
+        <v>455939</v>
       </c>
       <c r="R5" t="n">
-        <v>6836923</v>
+        <v>6836859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118614076</v>
+        <v>118614110</v>
       </c>
       <c r="B6" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456018</v>
+        <v>456021</v>
       </c>
       <c r="R6" t="n">
-        <v>6837020</v>
+        <v>6836968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118614106</v>
+        <v>118614093</v>
       </c>
       <c r="B7" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455886</v>
+        <v>456008</v>
       </c>
       <c r="R7" t="n">
-        <v>6836975</v>
+        <v>6837047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118614099</v>
+        <v>118614098</v>
       </c>
       <c r="B8" t="n">
         <v>78227</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455969</v>
+        <v>455984</v>
       </c>
       <c r="R8" t="n">
-        <v>6836868</v>
+        <v>6836875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118614077</v>
+        <v>118614087</v>
       </c>
       <c r="B9" t="n">
-        <v>79109</v>
+        <v>78590</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456008</v>
+        <v>455959</v>
       </c>
       <c r="R9" t="n">
-        <v>6836969</v>
+        <v>6837052</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118614089</v>
+        <v>118614105</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,42 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456021</v>
+        <v>455881</v>
       </c>
       <c r="R10" t="n">
-        <v>6837003</v>
+        <v>6836923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118614097</v>
+        <v>118614109</v>
       </c>
       <c r="B11" t="n">
         <v>78227</v>
@@ -1646,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456025</v>
+        <v>456008</v>
       </c>
       <c r="R11" t="n">
-        <v>6836910</v>
+        <v>6837047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118614083</v>
+        <v>118614084</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>79080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455947</v>
+        <v>456032</v>
       </c>
       <c r="R12" t="n">
-        <v>6837045</v>
+        <v>6836895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118614110</v>
+        <v>118614081</v>
       </c>
       <c r="B13" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456021</v>
+        <v>455942</v>
       </c>
       <c r="R13" t="n">
-        <v>6836968</v>
+        <v>6837031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118614103</v>
+        <v>118614086</v>
       </c>
       <c r="B14" t="n">
-        <v>78227</v>
+        <v>78590</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455886</v>
+        <v>455907</v>
       </c>
       <c r="R14" t="n">
-        <v>6836900</v>
+        <v>6837012</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118614081</v>
+        <v>118614092</v>
       </c>
       <c r="B15" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455942</v>
+        <v>455960</v>
       </c>
       <c r="R15" t="n">
-        <v>6837031</v>
+        <v>6837047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118614092</v>
+        <v>118614108</v>
       </c>
       <c r="B16" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118614084</v>
+        <v>118614077</v>
       </c>
       <c r="B17" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456032</v>
+        <v>456008</v>
       </c>
       <c r="R17" t="n">
-        <v>6836895</v>
+        <v>6836969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118614095</v>
+        <v>118614089</v>
       </c>
       <c r="B18" t="n">
-        <v>78227</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2336,34 +2323,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455985</v>
+        <v>456021</v>
       </c>
       <c r="R18" t="n">
-        <v>6836979</v>
+        <v>6837003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,6 +2391,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2422,7 +2422,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118614108</v>
+        <v>118614107</v>
       </c>
       <c r="B19" t="n">
         <v>78227</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455960</v>
+        <v>455942</v>
       </c>
       <c r="R19" t="n">
-        <v>6837047</v>
+        <v>6836999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118614093</v>
+        <v>118614088</v>
       </c>
       <c r="B20" t="n">
-        <v>78228</v>
+        <v>57443</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,21 +2540,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456008</v>
+        <v>455935</v>
       </c>
       <c r="R20" t="n">
-        <v>6837047</v>
+        <v>6836858</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118614088</v>
+        <v>118614083</v>
       </c>
       <c r="B21" t="n">
-        <v>57443</v>
+        <v>79109</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455935</v>
+        <v>455947</v>
       </c>
       <c r="R21" t="n">
-        <v>6836858</v>
+        <v>6837045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118614079</v>
+        <v>118614078</v>
       </c>
       <c r="B22" t="n">
         <v>79109</v>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455886</v>
+        <v>455889</v>
       </c>
       <c r="R22" t="n">
-        <v>6836900</v>
+        <v>6836903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118614100</v>
+        <v>118614096</v>
       </c>
       <c r="B23" t="n">
         <v>78227</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455939</v>
+        <v>456010</v>
       </c>
       <c r="R23" t="n">
-        <v>6836859</v>
+        <v>6836965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118614109</v>
+        <v>118614101</v>
       </c>
       <c r="B25" t="n">
         <v>78227</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456008</v>
+        <v>455923</v>
       </c>
       <c r="R25" t="n">
-        <v>6837047</v>
+        <v>6836875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118614087</v>
+        <v>118614104</v>
       </c>
       <c r="B26" t="n">
-        <v>78590</v>
+        <v>78227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455959</v>
+        <v>455867</v>
       </c>
       <c r="R26" t="n">
-        <v>6837052</v>
+        <v>6836907</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118614078</v>
+        <v>118614091</v>
       </c>
       <c r="B27" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455889</v>
+        <v>455881</v>
       </c>
       <c r="R27" t="n">
-        <v>6836903</v>
+        <v>6836923</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118614111</v>
+        <v>118614099</v>
       </c>
       <c r="B28" t="n">
-        <v>78136</v>
+        <v>78227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455971</v>
+        <v>455969</v>
       </c>
       <c r="R28" t="n">
-        <v>6837047</v>
+        <v>6836868</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118614104</v>
+        <v>118614111</v>
       </c>
       <c r="B29" t="n">
-        <v>78227</v>
+        <v>78136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455867</v>
+        <v>455971</v>
       </c>
       <c r="R29" t="n">
-        <v>6836907</v>
+        <v>6837047</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118614098</v>
+        <v>118614106</v>
       </c>
       <c r="B30" t="n">
         <v>78227</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455984</v>
+        <v>455886</v>
       </c>
       <c r="R30" t="n">
-        <v>6836875</v>
+        <v>6836975</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118614086</v>
+        <v>118614095</v>
       </c>
       <c r="B31" t="n">
-        <v>78590</v>
+        <v>78227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3662,21 +3662,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455907</v>
+        <v>455985</v>
       </c>
       <c r="R31" t="n">
-        <v>6837012</v>
+        <v>6836979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118614082</v>
+        <v>118614076</v>
       </c>
       <c r="B32" t="n">
-        <v>79109</v>
+        <v>78525</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455942</v>
+        <v>456018</v>
       </c>
       <c r="R32" t="n">
-        <v>6837052</v>
+        <v>6837020</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118614090</v>
+        <v>118614082</v>
       </c>
       <c r="B33" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455935</v>
+        <v>455942</v>
       </c>
       <c r="R33" t="n">
-        <v>6836857</v>
+        <v>6837052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118614105</v>
+        <v>118614090</v>
       </c>
       <c r="B34" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455881</v>
+        <v>455935</v>
       </c>
       <c r="R34" t="n">
-        <v>6836923</v>
+        <v>6836857</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118727600</v>
+        <v>118727518</v>
       </c>
       <c r="B35" t="n">
-        <v>80448</v>
+        <v>79109</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4070,34 +4070,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455702</v>
+        <v>455952</v>
       </c>
       <c r="R35" t="n">
-        <v>6837084</v>
+        <v>6836992</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4156,7 +4157,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118727622</v>
+        <v>118727631</v>
       </c>
       <c r="B36" t="n">
         <v>78491</v>
@@ -4196,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455747</v>
+        <v>455914</v>
       </c>
       <c r="R36" t="n">
-        <v>6837101</v>
+        <v>6836965</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,10 +4259,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118727640</v>
+        <v>118727610</v>
       </c>
       <c r="B37" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4274,21 +4275,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455987</v>
+        <v>455955</v>
       </c>
       <c r="R37" t="n">
-        <v>6836765</v>
+        <v>6837009</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118727582</v>
+        <v>118727620</v>
       </c>
       <c r="B38" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4376,42 +4377,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455915</v>
+        <v>455733</v>
       </c>
       <c r="R38" t="n">
-        <v>6836954</v>
+        <v>6837103</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4444,11 +4437,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4475,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118727523</v>
+        <v>118727604</v>
       </c>
       <c r="B39" t="n">
-        <v>79109</v>
+        <v>78227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4491,35 +4479,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455933</v>
+        <v>455931</v>
       </c>
       <c r="R39" t="n">
-        <v>6836859</v>
+        <v>6836858</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4578,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118727612</v>
+        <v>118727539</v>
       </c>
       <c r="B40" t="n">
-        <v>90661</v>
+        <v>79109</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4590,38 +4577,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455930</v>
+        <v>456035</v>
       </c>
       <c r="R40" t="n">
-        <v>6836843</v>
+        <v>6836794</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4680,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118727624</v>
+        <v>118727511</v>
       </c>
       <c r="B41" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4696,34 +4684,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455844</v>
+        <v>455951</v>
       </c>
       <c r="R41" t="n">
-        <v>6837118</v>
+        <v>6836741</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4782,10 +4771,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118727581</v>
+        <v>118727658</v>
       </c>
       <c r="B42" t="n">
-        <v>57290</v>
+        <v>78136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4798,42 +4787,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455926</v>
+        <v>455957</v>
       </c>
       <c r="R42" t="n">
-        <v>6836949</v>
+        <v>6836744</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,11 +4847,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4897,10 +4873,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118727550</v>
+        <v>118727612</v>
       </c>
       <c r="B43" t="n">
-        <v>79080</v>
+        <v>90661</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,39 +4885,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455970</v>
+        <v>455930</v>
       </c>
       <c r="R43" t="n">
-        <v>6836763</v>
+        <v>6836843</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,10 +4975,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118727543</v>
+        <v>118727585</v>
       </c>
       <c r="B44" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5016,35 +4991,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456050</v>
+        <v>455930</v>
       </c>
       <c r="R44" t="n">
-        <v>6836858</v>
+        <v>6836897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5077,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118727606</v>
+        <v>118727550</v>
       </c>
       <c r="B45" t="n">
-        <v>78227</v>
+        <v>79080</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5119,34 +5093,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456025</v>
+        <v>455970</v>
       </c>
       <c r="R45" t="n">
-        <v>6836801</v>
+        <v>6836763</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5205,7 +5180,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118727623</v>
+        <v>118727629</v>
       </c>
       <c r="B46" t="n">
         <v>78491</v>
@@ -5245,10 +5220,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455802</v>
+        <v>455870</v>
       </c>
       <c r="R46" t="n">
-        <v>6837089</v>
+        <v>6837153</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,7 +5282,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118727537</v>
+        <v>118727542</v>
       </c>
       <c r="B47" t="n">
         <v>79109</v>
@@ -5348,10 +5323,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456027</v>
+        <v>456022</v>
       </c>
       <c r="R47" t="n">
-        <v>6836806</v>
+        <v>6836819</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5410,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118727658</v>
+        <v>118727606</v>
       </c>
       <c r="B48" t="n">
-        <v>78136</v>
+        <v>78227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5426,21 +5401,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5450,10 +5425,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455957</v>
+        <v>456025</v>
       </c>
       <c r="R48" t="n">
-        <v>6836744</v>
+        <v>6836801</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,10 +5487,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118727545</v>
+        <v>118727582</v>
       </c>
       <c r="B49" t="n">
-        <v>79080</v>
+        <v>57290</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5528,35 +5503,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455700</v>
+        <v>455915</v>
       </c>
       <c r="R49" t="n">
-        <v>6837083</v>
+        <v>6836954</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5589,6 +5571,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2-3 år gamla ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5615,10 +5602,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118727590</v>
+        <v>118727558</v>
       </c>
       <c r="B50" t="n">
-        <v>78228</v>
+        <v>78590</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5631,34 +5618,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455955</v>
+        <v>456036</v>
       </c>
       <c r="R50" t="n">
-        <v>6836833</v>
+        <v>6836794</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5699,6 +5697,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5717,10 +5716,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118727549</v>
+        <v>118727594</v>
       </c>
       <c r="B51" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5733,35 +5732,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455956</v>
+        <v>456008</v>
       </c>
       <c r="R51" t="n">
-        <v>6836745</v>
+        <v>6836969</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,7 +5818,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118727586</v>
+        <v>118727598</v>
       </c>
       <c r="B52" t="n">
         <v>78228</v>
@@ -5860,10 +5858,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455865</v>
+        <v>455878</v>
       </c>
       <c r="R52" t="n">
-        <v>6836943</v>
+        <v>6836925</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,7 +5920,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118727588</v>
+        <v>118727593</v>
       </c>
       <c r="B53" t="n">
         <v>78228</v>
@@ -5962,10 +5960,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455938</v>
+        <v>456027</v>
       </c>
       <c r="R53" t="n">
-        <v>6836861</v>
+        <v>6836806</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6024,10 +6022,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118727562</v>
+        <v>118727547</v>
       </c>
       <c r="B54" t="n">
-        <v>78590</v>
+        <v>79080</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6040,34 +6038,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455956</v>
+        <v>455904</v>
       </c>
       <c r="R54" t="n">
-        <v>6836833</v>
+        <v>6836778</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6126,10 +6125,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118727560</v>
+        <v>118727503</v>
       </c>
       <c r="B55" t="n">
-        <v>78590</v>
+        <v>78525</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6142,45 +6141,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455904</v>
+        <v>456028</v>
       </c>
       <c r="R55" t="n">
-        <v>6836777</v>
+        <v>6836799</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6221,7 +6209,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6240,10 +6227,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118727620</v>
+        <v>118727652</v>
       </c>
       <c r="B56" t="n">
-        <v>78491</v>
+        <v>94520</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6252,25 +6239,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6280,10 +6267,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455733</v>
+        <v>455841</v>
       </c>
       <c r="R56" t="n">
-        <v>6837103</v>
+        <v>6837101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6342,7 +6329,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118727520</v>
+        <v>118727541</v>
       </c>
       <c r="B57" t="n">
         <v>79109</v>
@@ -6383,10 +6370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455867</v>
+        <v>456048</v>
       </c>
       <c r="R57" t="n">
-        <v>6836942</v>
+        <v>6836813</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6445,7 +6432,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118727533</v>
+        <v>118727528</v>
       </c>
       <c r="B58" t="n">
         <v>79109</v>
@@ -6486,10 +6473,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455956</v>
+        <v>455898</v>
       </c>
       <c r="R58" t="n">
-        <v>6836745</v>
+        <v>6836767</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6548,10 +6535,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118727665</v>
+        <v>118727565</v>
       </c>
       <c r="B59" t="n">
-        <v>77875</v>
+        <v>57443</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6564,21 +6551,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6588,10 +6575,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455701</v>
+        <v>455864</v>
       </c>
       <c r="R59" t="n">
-        <v>6837084</v>
+        <v>6837158</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6650,10 +6637,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118727541</v>
+        <v>118727611</v>
       </c>
       <c r="B60" t="n">
-        <v>79109</v>
+        <v>90661</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,39 +6649,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456048</v>
+        <v>455716</v>
       </c>
       <c r="R60" t="n">
-        <v>6836813</v>
+        <v>6837046</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6753,10 +6739,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118727611</v>
+        <v>118727603</v>
       </c>
       <c r="B61" t="n">
-        <v>90661</v>
+        <v>80448</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6765,25 +6751,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6793,10 +6779,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455716</v>
+        <v>456024</v>
       </c>
       <c r="R61" t="n">
-        <v>6837046</v>
+        <v>6836818</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118727592</v>
+        <v>118727544</v>
       </c>
       <c r="B62" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6871,34 +6857,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456025</v>
+        <v>456065</v>
       </c>
       <c r="R62" t="n">
-        <v>6836800</v>
+        <v>6836867</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,7 +6944,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118727527</v>
+        <v>118727530</v>
       </c>
       <c r="B63" t="n">
         <v>79109</v>
@@ -6998,10 +6985,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455903</v>
+        <v>455892</v>
       </c>
       <c r="R63" t="n">
-        <v>6836778</v>
+        <v>6836753</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7060,10 +7047,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118727619</v>
+        <v>118727553</v>
       </c>
       <c r="B64" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7076,34 +7063,35 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455726</v>
+        <v>456026</v>
       </c>
       <c r="R64" t="n">
-        <v>6837099</v>
+        <v>6836798</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7162,10 +7150,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118727635</v>
+        <v>118727549</v>
       </c>
       <c r="B65" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7178,34 +7166,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455915</v>
+        <v>455956</v>
       </c>
       <c r="R65" t="n">
-        <v>6836927</v>
+        <v>6836745</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7264,10 +7253,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118727542</v>
+        <v>118727507</v>
       </c>
       <c r="B66" t="n">
-        <v>79109</v>
+        <v>78525</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7280,21 +7269,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7305,10 +7294,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456022</v>
+        <v>455726</v>
       </c>
       <c r="R66" t="n">
-        <v>6836819</v>
+        <v>6837099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7367,10 +7356,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118727524</v>
+        <v>118727510</v>
       </c>
       <c r="B67" t="n">
-        <v>79109</v>
+        <v>78525</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7383,21 +7372,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7408,10 +7397,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455955</v>
+        <v>455912</v>
       </c>
       <c r="R67" t="n">
-        <v>6836833</v>
+        <v>6836969</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7470,10 +7459,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118727539</v>
+        <v>118727639</v>
       </c>
       <c r="B68" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7486,35 +7475,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>456035</v>
+        <v>455967</v>
       </c>
       <c r="R68" t="n">
-        <v>6836794</v>
+        <v>6836746</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7573,10 +7561,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118727553</v>
+        <v>118727633</v>
       </c>
       <c r="B69" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7589,35 +7577,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>456026</v>
+        <v>455917</v>
       </c>
       <c r="R69" t="n">
-        <v>6836798</v>
+        <v>6836957</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7676,10 +7663,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118727660</v>
+        <v>118727662</v>
       </c>
       <c r="B70" t="n">
-        <v>78136</v>
+        <v>77423</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7692,21 +7679,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7716,10 +7703,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>456065</v>
+        <v>455700</v>
       </c>
       <c r="R70" t="n">
-        <v>6836867</v>
+        <v>6837084</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7778,10 +7765,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118727607</v>
+        <v>118727581</v>
       </c>
       <c r="B71" t="n">
-        <v>78227</v>
+        <v>57290</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7794,34 +7781,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>456027</v>
+        <v>455926</v>
       </c>
       <c r="R71" t="n">
-        <v>6836806</v>
+        <v>6836949</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7854,6 +7849,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7880,7 +7880,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118727587</v>
+        <v>118727595</v>
       </c>
       <c r="B72" t="n">
         <v>78228</v>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455933</v>
+        <v>455986</v>
       </c>
       <c r="R72" t="n">
-        <v>6836859</v>
+        <v>6836980</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7982,7 +7982,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118727558</v>
+        <v>118727562</v>
       </c>
       <c r="B73" t="n">
         <v>78590</v>
@@ -8015,28 +8015,17 @@
           <t>(L.) Hue</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>456036</v>
+        <v>455956</v>
       </c>
       <c r="R73" t="n">
-        <v>6836794</v>
+        <v>6836833</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8077,7 +8066,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8096,10 +8084,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118727653</v>
+        <v>118727513</v>
       </c>
       <c r="B74" t="n">
-        <v>94520</v>
+        <v>78525</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8108,38 +8096,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2170</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>456022</v>
+        <v>455971</v>
       </c>
       <c r="R74" t="n">
-        <v>6836970</v>
+        <v>6836747</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8198,10 +8187,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118727608</v>
+        <v>118727601</v>
       </c>
       <c r="B75" t="n">
-        <v>78227</v>
+        <v>80448</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8214,21 +8203,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8238,10 +8227,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>456041</v>
+        <v>455913</v>
       </c>
       <c r="R75" t="n">
-        <v>6836795</v>
+        <v>6836820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8300,10 +8289,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118727591</v>
+        <v>118727519</v>
       </c>
       <c r="B76" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8316,34 +8305,35 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455924</v>
+        <v>455850</v>
       </c>
       <c r="R76" t="n">
-        <v>6836800</v>
+        <v>6837094</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8402,10 +8392,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118727556</v>
+        <v>118727622</v>
       </c>
       <c r="B77" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8418,35 +8408,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>456028</v>
+        <v>455747</v>
       </c>
       <c r="R77" t="n">
-        <v>6836813</v>
+        <v>6837101</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8505,10 +8494,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118727598</v>
+        <v>118727524</v>
       </c>
       <c r="B78" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8521,34 +8510,35 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455878</v>
+        <v>455955</v>
       </c>
       <c r="R78" t="n">
-        <v>6836925</v>
+        <v>6836833</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8607,10 +8597,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118727548</v>
+        <v>118727664</v>
       </c>
       <c r="B79" t="n">
-        <v>79080</v>
+        <v>77423</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8623,35 +8613,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455926</v>
+        <v>456028</v>
       </c>
       <c r="R79" t="n">
-        <v>6836752</v>
+        <v>6836814</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8710,10 +8699,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118727554</v>
+        <v>118727579</v>
       </c>
       <c r="B80" t="n">
-        <v>79080</v>
+        <v>78580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8722,39 +8711,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6450</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>456036</v>
+        <v>455885</v>
       </c>
       <c r="R80" t="n">
-        <v>6836795</v>
+        <v>6836936</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8813,10 +8801,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118727585</v>
+        <v>118727609</v>
       </c>
       <c r="B81" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8829,21 +8817,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8853,10 +8841,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455930</v>
+        <v>456053</v>
       </c>
       <c r="R81" t="n">
-        <v>6836897</v>
+        <v>6836858</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8915,10 +8903,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118727596</v>
+        <v>118727648</v>
       </c>
       <c r="B82" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8931,21 +8919,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8955,10 +8943,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>455956</v>
+        <v>456055</v>
       </c>
       <c r="R82" t="n">
-        <v>6837009</v>
+        <v>6836875</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9017,10 +9005,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118727599</v>
+        <v>118727632</v>
       </c>
       <c r="B83" t="n">
-        <v>90973</v>
+        <v>78491</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9033,21 +9021,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9057,10 +9045,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>455957</v>
+        <v>455916</v>
       </c>
       <c r="R83" t="n">
-        <v>6836745</v>
+        <v>6836963</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9119,10 +9107,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118727503</v>
+        <v>118727531</v>
       </c>
       <c r="B84" t="n">
-        <v>78525</v>
+        <v>79109</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9135,34 +9123,35 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>456028</v>
+        <v>455918</v>
       </c>
       <c r="R84" t="n">
-        <v>6836799</v>
+        <v>6836750</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9221,10 +9210,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118727629</v>
+        <v>118727537</v>
       </c>
       <c r="B85" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9237,34 +9226,35 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>455870</v>
+        <v>456027</v>
       </c>
       <c r="R85" t="n">
-        <v>6837153</v>
+        <v>6836806</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9323,10 +9313,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118727529</v>
+        <v>118727554</v>
       </c>
       <c r="B86" t="n">
-        <v>79109</v>
+        <v>79080</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9339,21 +9329,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9354,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>455885</v>
+        <v>456036</v>
       </c>
       <c r="R86" t="n">
-        <v>6836757</v>
+        <v>6836795</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9426,10 +9416,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118727521</v>
+        <v>118727584</v>
       </c>
       <c r="B87" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9442,35 +9432,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>455919</v>
+        <v>456053</v>
       </c>
       <c r="R87" t="n">
-        <v>6836937</v>
+        <v>6836858</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9529,7 +9518,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118727637</v>
+        <v>118727630</v>
       </c>
       <c r="B88" t="n">
         <v>78491</v>
@@ -9569,10 +9558,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455922</v>
+        <v>455860</v>
       </c>
       <c r="R88" t="n">
-        <v>6836913</v>
+        <v>6837129</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9631,10 +9620,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118727557</v>
+        <v>118727591</v>
       </c>
       <c r="B89" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9647,35 +9636,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>456053</v>
+        <v>455924</v>
       </c>
       <c r="R89" t="n">
-        <v>6836858</v>
+        <v>6836800</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9734,10 +9722,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118727547</v>
+        <v>118727538</v>
       </c>
       <c r="B90" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9750,21 +9738,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9775,10 +9763,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455904</v>
+        <v>456041</v>
       </c>
       <c r="R90" t="n">
-        <v>6836778</v>
+        <v>6836794</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9837,10 +9825,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118727526</v>
+        <v>118727653</v>
       </c>
       <c r="B91" t="n">
-        <v>79109</v>
+        <v>94520</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9849,39 +9837,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>455943</v>
+        <v>456022</v>
       </c>
       <c r="R91" t="n">
-        <v>6836795</v>
+        <v>6836970</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9940,10 +9927,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118727530</v>
+        <v>118727624</v>
       </c>
       <c r="B92" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9956,35 +9943,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>455892</v>
+        <v>455844</v>
       </c>
       <c r="R92" t="n">
-        <v>6836753</v>
+        <v>6837118</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10043,10 +10029,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118727510</v>
+        <v>118727668</v>
       </c>
       <c r="B93" t="n">
-        <v>78525</v>
+        <v>77875</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10059,35 +10045,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>455912</v>
+        <v>456028</v>
       </c>
       <c r="R93" t="n">
-        <v>6836969</v>
+        <v>6836814</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10146,10 +10131,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118727508</v>
+        <v>118727617</v>
       </c>
       <c r="B94" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10162,35 +10147,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>455765</v>
+        <v>455720</v>
       </c>
       <c r="R94" t="n">
-        <v>6837108</v>
+        <v>6837077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10249,10 +10233,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118727601</v>
+        <v>118727588</v>
       </c>
       <c r="B95" t="n">
-        <v>80448</v>
+        <v>78228</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10265,21 +10249,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10289,10 +10273,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455913</v>
+        <v>455938</v>
       </c>
       <c r="R95" t="n">
-        <v>6836820</v>
+        <v>6836861</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10351,10 +10335,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118727532</v>
+        <v>118727590</v>
       </c>
       <c r="B96" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10367,35 +10351,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455926</v>
+        <v>455955</v>
       </c>
       <c r="R96" t="n">
-        <v>6836752</v>
+        <v>6836833</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10454,10 +10437,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118727518</v>
+        <v>118727556</v>
       </c>
       <c r="B97" t="n">
-        <v>79109</v>
+        <v>79080</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10470,21 +10453,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10495,10 +10478,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455952</v>
+        <v>456028</v>
       </c>
       <c r="R97" t="n">
-        <v>6836992</v>
+        <v>6836813</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10557,10 +10540,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118727544</v>
+        <v>118727625</v>
       </c>
       <c r="B98" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10573,35 +10556,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>456065</v>
+        <v>455868</v>
       </c>
       <c r="R98" t="n">
-        <v>6836867</v>
+        <v>6837146</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10660,10 +10642,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118727579</v>
+        <v>118727520</v>
       </c>
       <c r="B99" t="n">
-        <v>78580</v>
+        <v>79109</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10672,38 +10654,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455885</v>
+        <v>455867</v>
       </c>
       <c r="R99" t="n">
-        <v>6836936</v>
+        <v>6836942</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10762,10 +10745,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118727630</v>
+        <v>118727521</v>
       </c>
       <c r="B100" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10778,34 +10761,35 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455860</v>
+        <v>455919</v>
       </c>
       <c r="R100" t="n">
-        <v>6837129</v>
+        <v>6836937</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10864,7 +10848,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118727617</v>
+        <v>118727638</v>
       </c>
       <c r="B101" t="n">
         <v>78491</v>
@@ -10904,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455720</v>
+        <v>455933</v>
       </c>
       <c r="R101" t="n">
-        <v>6837077</v>
+        <v>6836917</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10966,10 +10950,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118727511</v>
+        <v>118727548</v>
       </c>
       <c r="B102" t="n">
-        <v>78525</v>
+        <v>79080</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10982,21 +10966,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11007,10 +10991,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455951</v>
+        <v>455926</v>
       </c>
       <c r="R102" t="n">
-        <v>6836741</v>
+        <v>6836752</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11069,10 +11053,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118727502</v>
+        <v>118727586</v>
       </c>
       <c r="B103" t="n">
-        <v>78525</v>
+        <v>78228</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,21 +11069,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11093,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>456023</v>
+        <v>455865</v>
       </c>
       <c r="R103" t="n">
-        <v>6836783</v>
+        <v>6836943</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11171,10 +11155,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118727604</v>
+        <v>118727600</v>
       </c>
       <c r="B104" t="n">
-        <v>78227</v>
+        <v>80448</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11187,21 +11171,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11195,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>455931</v>
+        <v>455702</v>
       </c>
       <c r="R104" t="n">
-        <v>6836858</v>
+        <v>6837084</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11273,10 +11257,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118727632</v>
+        <v>118727557</v>
       </c>
       <c r="B105" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,34 +11273,35 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455916</v>
+        <v>456053</v>
       </c>
       <c r="R105" t="n">
-        <v>6836963</v>
+        <v>6836858</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11375,10 +11360,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118727655</v>
+        <v>118727506</v>
       </c>
       <c r="B106" t="n">
-        <v>78136</v>
+        <v>78525</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11391,34 +11376,35 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455973</v>
+        <v>455726</v>
       </c>
       <c r="R106" t="n">
-        <v>6836775</v>
+        <v>6837083</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11477,10 +11463,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118727652</v>
+        <v>118727619</v>
       </c>
       <c r="B107" t="n">
-        <v>94520</v>
+        <v>78491</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11489,25 +11475,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11517,10 +11503,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455841</v>
+        <v>455726</v>
       </c>
       <c r="R107" t="n">
-        <v>6837101</v>
+        <v>6837099</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11579,10 +11565,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118727625</v>
+        <v>118727665</v>
       </c>
       <c r="B108" t="n">
-        <v>78491</v>
+        <v>77875</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11595,21 +11581,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11619,10 +11605,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>455868</v>
+        <v>455701</v>
       </c>
       <c r="R108" t="n">
-        <v>6837146</v>
+        <v>6837084</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11681,10 +11667,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118727610</v>
+        <v>118727618</v>
       </c>
       <c r="B109" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11697,21 +11683,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11721,10 +11707,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>455955</v>
+        <v>455724</v>
       </c>
       <c r="R109" t="n">
-        <v>6837009</v>
+        <v>6837080</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11783,10 +11769,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118727618</v>
+        <v>118727667</v>
       </c>
       <c r="B110" t="n">
-        <v>78491</v>
+        <v>77875</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11799,21 +11785,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11823,10 +11809,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>455724</v>
+        <v>456035</v>
       </c>
       <c r="R110" t="n">
-        <v>6837080</v>
+        <v>6836796</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11885,10 +11871,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118727667</v>
+        <v>118727626</v>
       </c>
       <c r="B111" t="n">
-        <v>77875</v>
+        <v>78491</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11901,21 +11887,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11925,10 +11911,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>456035</v>
+        <v>455897</v>
       </c>
       <c r="R111" t="n">
-        <v>6836796</v>
+        <v>6836935</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11987,7 +11973,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118727636</v>
+        <v>118727640</v>
       </c>
       <c r="B112" t="n">
         <v>78491</v>
@@ -12027,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455925</v>
+        <v>455987</v>
       </c>
       <c r="R112" t="n">
-        <v>6836919</v>
+        <v>6836765</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12089,10 +12075,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118727603</v>
+        <v>118727635</v>
       </c>
       <c r="B113" t="n">
-        <v>80448</v>
+        <v>78491</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12105,21 +12091,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12129,10 +12115,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>456024</v>
+        <v>455915</v>
       </c>
       <c r="R113" t="n">
-        <v>6836818</v>
+        <v>6836927</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12191,10 +12177,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118727595</v>
+        <v>118727651</v>
       </c>
       <c r="B114" t="n">
-        <v>78228</v>
+        <v>90756</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12203,25 +12189,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12231,10 +12217,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455986</v>
+        <v>455972</v>
       </c>
       <c r="R114" t="n">
-        <v>6836980</v>
+        <v>6836775</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12293,10 +12279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118727664</v>
+        <v>118727508</v>
       </c>
       <c r="B115" t="n">
-        <v>77423</v>
+        <v>78525</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12309,34 +12295,35 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>456028</v>
+        <v>455765</v>
       </c>
       <c r="R115" t="n">
-        <v>6836814</v>
+        <v>6837108</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12395,10 +12382,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118727651</v>
+        <v>118727546</v>
       </c>
       <c r="B116" t="n">
-        <v>90756</v>
+        <v>79080</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12407,38 +12394,39 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455972</v>
+        <v>455932</v>
       </c>
       <c r="R116" t="n">
-        <v>6836775</v>
+        <v>6836858</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12497,7 +12485,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118727594</v>
+        <v>118727592</v>
       </c>
       <c r="B117" t="n">
         <v>78228</v>
@@ -12537,10 +12525,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>456008</v>
+        <v>456025</v>
       </c>
       <c r="R117" t="n">
-        <v>6836969</v>
+        <v>6836800</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12599,10 +12587,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118727626</v>
+        <v>118727560</v>
       </c>
       <c r="B118" t="n">
-        <v>78491</v>
+        <v>78590</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12615,34 +12603,45 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455897</v>
+        <v>455904</v>
       </c>
       <c r="R118" t="n">
-        <v>6836935</v>
+        <v>6836777</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12683,6 +12682,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12701,10 +12701,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118727639</v>
+        <v>118727587</v>
       </c>
       <c r="B119" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12717,21 +12717,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455967</v>
+        <v>455933</v>
       </c>
       <c r="R119" t="n">
-        <v>6836746</v>
+        <v>6836859</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12803,10 +12803,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118727506</v>
+        <v>118727545</v>
       </c>
       <c r="B120" t="n">
-        <v>78525</v>
+        <v>79080</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12819,21 +12819,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12844,7 +12844,7 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455726</v>
+        <v>455700</v>
       </c>
       <c r="R120" t="n">
         <v>6837083</v>
@@ -12906,10 +12906,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118727513</v>
+        <v>118727597</v>
       </c>
       <c r="B121" t="n">
-        <v>78525</v>
+        <v>78228</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,35 +12922,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455971</v>
+        <v>455943</v>
       </c>
       <c r="R121" t="n">
-        <v>6836747</v>
+        <v>6836998</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13009,10 +13008,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118727593</v>
+        <v>118727608</v>
       </c>
       <c r="B122" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13025,21 +13024,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13049,10 +13048,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>456027</v>
+        <v>456041</v>
       </c>
       <c r="R122" t="n">
-        <v>6836806</v>
+        <v>6836795</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13111,10 +13110,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118727633</v>
+        <v>118727523</v>
       </c>
       <c r="B123" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13127,34 +13126,35 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>455917</v>
+        <v>455933</v>
       </c>
       <c r="R123" t="n">
-        <v>6836957</v>
+        <v>6836859</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13213,7 +13213,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118727528</v>
+        <v>118727525</v>
       </c>
       <c r="B124" t="n">
         <v>79109</v>
@@ -13254,10 +13254,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>455898</v>
+        <v>455924</v>
       </c>
       <c r="R124" t="n">
-        <v>6836767</v>
+        <v>6836801</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13316,10 +13316,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118727583</v>
+        <v>118727532</v>
       </c>
       <c r="B125" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13332,34 +13332,35 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>456050</v>
+        <v>455926</v>
       </c>
       <c r="R125" t="n">
-        <v>6836858</v>
+        <v>6836752</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13418,10 +13419,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118727609</v>
+        <v>118727543</v>
       </c>
       <c r="B126" t="n">
-        <v>78227</v>
+        <v>79109</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13434,31 +13435,32 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>456053</v>
+        <v>456050</v>
       </c>
       <c r="R126" t="n">
         <v>6836858</v>
@@ -13520,7 +13522,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118727519</v>
+        <v>118727527</v>
       </c>
       <c r="B127" t="n">
         <v>79109</v>
@@ -13561,10 +13563,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455850</v>
+        <v>455903</v>
       </c>
       <c r="R127" t="n">
-        <v>6837094</v>
+        <v>6836778</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13623,10 +13625,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118727668</v>
+        <v>118727529</v>
       </c>
       <c r="B128" t="n">
-        <v>77875</v>
+        <v>79109</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13639,34 +13641,35 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>456028</v>
+        <v>455885</v>
       </c>
       <c r="R128" t="n">
-        <v>6836814</v>
+        <v>6836757</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13725,10 +13728,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118727561</v>
+        <v>118727607</v>
       </c>
       <c r="B129" t="n">
-        <v>78590</v>
+        <v>78227</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13741,21 +13744,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13765,10 +13768,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>455930</v>
+        <v>456027</v>
       </c>
       <c r="R129" t="n">
-        <v>6836890</v>
+        <v>6836806</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13827,7 +13830,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118727631</v>
+        <v>118727627</v>
       </c>
       <c r="B130" t="n">
         <v>78491</v>
@@ -13867,10 +13870,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455914</v>
+        <v>455891</v>
       </c>
       <c r="R130" t="n">
-        <v>6836965</v>
+        <v>6836950</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13929,10 +13932,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118727662</v>
+        <v>118727660</v>
       </c>
       <c r="B131" t="n">
-        <v>77423</v>
+        <v>78136</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13945,21 +13948,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13969,10 +13972,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455700</v>
+        <v>456065</v>
       </c>
       <c r="R131" t="n">
-        <v>6837084</v>
+        <v>6836867</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14031,10 +14034,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118727638</v>
+        <v>118727502</v>
       </c>
       <c r="B132" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14047,21 +14050,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14071,10 +14074,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455933</v>
+        <v>456023</v>
       </c>
       <c r="R132" t="n">
-        <v>6836917</v>
+        <v>6836783</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14133,10 +14136,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118727531</v>
+        <v>118727636</v>
       </c>
       <c r="B133" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14149,35 +14152,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455918</v>
+        <v>455925</v>
       </c>
       <c r="R133" t="n">
-        <v>6836750</v>
+        <v>6836919</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14236,10 +14238,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118727584</v>
+        <v>118727599</v>
       </c>
       <c r="B134" t="n">
-        <v>78228</v>
+        <v>90973</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,21 +14254,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>5467</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14276,10 +14278,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>456053</v>
+        <v>455957</v>
       </c>
       <c r="R134" t="n">
-        <v>6836858</v>
+        <v>6836745</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14338,10 +14340,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118727627</v>
+        <v>118727561</v>
       </c>
       <c r="B135" t="n">
-        <v>78491</v>
+        <v>78590</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14354,21 +14356,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14378,10 +14380,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455891</v>
+        <v>455930</v>
       </c>
       <c r="R135" t="n">
-        <v>6836950</v>
+        <v>6836890</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14440,10 +14442,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118727525</v>
+        <v>118727583</v>
       </c>
       <c r="B136" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14456,35 +14458,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455924</v>
+        <v>456050</v>
       </c>
       <c r="R136" t="n">
-        <v>6836801</v>
+        <v>6836858</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14543,10 +14544,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118727507</v>
+        <v>118727526</v>
       </c>
       <c r="B137" t="n">
-        <v>78525</v>
+        <v>79109</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14559,21 +14560,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14584,10 +14585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455726</v>
+        <v>455943</v>
       </c>
       <c r="R137" t="n">
-        <v>6837099</v>
+        <v>6836795</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14646,10 +14647,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118727565</v>
+        <v>118727623</v>
       </c>
       <c r="B138" t="n">
-        <v>57443</v>
+        <v>78491</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14662,21 +14663,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14686,10 +14687,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455864</v>
+        <v>455802</v>
       </c>
       <c r="R138" t="n">
-        <v>6837158</v>
+        <v>6837089</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14851,10 +14852,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118727546</v>
+        <v>118727637</v>
       </c>
       <c r="B140" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14867,35 +14868,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455932</v>
+        <v>455922</v>
       </c>
       <c r="R140" t="n">
-        <v>6836858</v>
+        <v>6836913</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14954,10 +14954,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118727597</v>
+        <v>118727533</v>
       </c>
       <c r="B141" t="n">
-        <v>78228</v>
+        <v>79109</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14970,34 +14970,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455943</v>
+        <v>455956</v>
       </c>
       <c r="R141" t="n">
-        <v>6836998</v>
+        <v>6836745</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15056,10 +15057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118727648</v>
+        <v>118727655</v>
       </c>
       <c r="B142" t="n">
-        <v>78491</v>
+        <v>78136</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15072,21 +15073,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15096,10 +15097,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>456055</v>
+        <v>455973</v>
       </c>
       <c r="R142" t="n">
-        <v>6836875</v>
+        <v>6836775</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15158,10 +15159,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118727538</v>
+        <v>118727596</v>
       </c>
       <c r="B143" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15174,35 +15175,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Björtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>456041</v>
+        <v>455956</v>
       </c>
       <c r="R143" t="n">
-        <v>6836794</v>
+        <v>6837009</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -7752,12 +7752,7 @@
         <v>118727582</v>
       </c>
       <c r="B71" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57852</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7787,7 +7782,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -7752,7 +7752,7 @@
         <v>118727582</v>
       </c>
       <c r="B71" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -7752,7 +7752,7 @@
         <v>118727582</v>
       </c>
       <c r="B71" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -7752,7 +7752,7 @@
         <v>118727582</v>
       </c>
       <c r="B71" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -7752,7 +7752,7 @@
         <v>118727582</v>
       </c>
       <c r="B71" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 50145-2022 artfynd.xlsx
+++ b/artfynd/A 50145-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AZ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727502</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727503</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727505</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727506</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,6 +1491,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727507</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727508</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727509</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1745,6 +1800,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727510</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1843,6 +1903,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727511</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727513</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727514</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614111</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727655</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727656</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727657</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727658</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727659</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727660</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614085</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614086</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614087</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727558</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3227,6 +3357,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727560</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3324,6 +3459,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727561</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3421,6 +3561,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727562</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3518,6 +3663,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727600</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3615,6 +3765,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727601</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3712,6 +3867,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727603</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3809,6 +3969,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727611</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3906,6 +4071,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727612</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4003,6 +4173,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727652</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4100,6 +4275,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727653</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4197,6 +4377,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727599</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4294,6 +4479,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614110</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4391,6 +4581,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727614</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4488,6 +4683,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727615</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4585,6 +4785,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727616</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4682,6 +4887,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727617</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4779,6 +4989,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727618</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4876,6 +5091,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727619</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4973,6 +5193,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727620</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5070,6 +5295,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727622</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5167,6 +5397,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727623</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5264,6 +5499,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727624</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5361,6 +5601,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727625</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5458,6 +5703,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727626</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5555,6 +5805,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727627</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5652,6 +5907,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727628</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5749,6 +6009,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727629</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5846,6 +6111,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727630</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5943,6 +6213,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727631</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6040,6 +6315,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727632</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6137,6 +6417,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727633</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6234,6 +6519,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727635</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6331,6 +6621,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727636</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6428,6 +6723,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727637</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6525,6 +6825,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727638</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6622,6 +6927,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727639</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6719,6 +7029,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727640</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6816,6 +7131,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727641</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6913,6 +7233,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727642</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7010,6 +7335,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727644</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7107,6 +7437,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727645</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7204,6 +7539,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727646</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7301,6 +7641,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727648</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7398,6 +7743,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727650</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7495,6 +7845,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727665</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7592,6 +7947,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727666</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7689,6 +8049,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727667</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7786,6 +8151,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727668</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7883,6 +8253,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727501</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7980,6 +8355,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614095</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8077,6 +8457,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614096</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8174,6 +8559,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614097</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8271,6 +8661,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614098</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8368,6 +8763,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614099</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8465,6 +8865,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614100</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8562,6 +8967,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614101</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8659,6 +9069,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614102</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8756,6 +9171,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614103</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8853,6 +9273,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614104</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8950,6 +9375,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614105</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9047,6 +9477,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614106</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9144,6 +9579,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614107</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9241,6 +9681,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614108</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9338,6 +9783,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614109</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9435,6 +9885,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727604</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9532,6 +9987,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727605</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9629,6 +10089,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727606</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9726,6 +10191,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727607</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9823,6 +10293,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727608</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9920,6 +10395,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727609</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10017,6 +10497,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727610</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10114,6 +10599,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727579</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10211,6 +10701,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614077</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10308,6 +10803,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614078</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10405,6 +10905,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614079</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10502,6 +11007,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614081</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10599,6 +11109,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614082</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10696,6 +11211,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614083</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10794,6 +11314,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727517</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10892,6 +11417,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727518</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10990,6 +11520,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727519</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11088,6 +11623,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727520</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11186,6 +11726,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727521</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11284,6 +11829,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727523</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11382,6 +11932,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727524</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11480,6 +12035,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727525</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11578,6 +12138,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727526</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11676,6 +12241,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727527</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11774,6 +12344,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727528</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11872,6 +12447,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727529</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11970,6 +12550,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727530</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12068,6 +12653,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727531</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12166,6 +12756,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727532</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12264,6 +12859,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727533</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12362,6 +12962,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727534</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12460,6 +13065,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727537</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12558,6 +13168,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727538</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12656,6 +13271,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727539</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12754,6 +13374,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727541</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12852,6 +13477,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727542</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12950,6 +13580,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727543</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13048,6 +13683,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727544</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13145,6 +13785,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727662</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13242,6 +13887,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727663</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13339,6 +13989,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727664</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13449,6 +14104,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614089</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13559,6 +14219,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727581</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13669,6 +14334,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727582</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13766,6 +14436,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614088</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13863,6 +14538,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727565</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13960,6 +14640,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614090</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14057,6 +14742,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614091</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14154,6 +14844,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614092</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14251,6 +14946,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614093</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14348,6 +15048,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727583</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14445,6 +15150,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727584</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14542,6 +15252,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727585</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14639,6 +15354,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727586</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14736,6 +15456,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727587</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14833,6 +15558,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727588</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14930,6 +15660,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727590</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15027,6 +15762,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727591</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15124,6 +15864,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727592</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15221,6 +15966,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727593</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15318,6 +16068,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727594</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15415,6 +16170,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727595</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15512,6 +16272,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727596</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15609,6 +16374,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727597</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15706,6 +16476,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727598</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15803,6 +16578,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614084</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15901,6 +16681,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727545</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15999,6 +16784,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727546</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16097,6 +16887,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727547</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16195,6 +16990,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727548</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16293,6 +17093,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727549</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16391,6 +17196,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727550</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16489,6 +17299,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727552</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16587,6 +17402,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727553</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16685,6 +17505,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727554</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16783,6 +17608,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727556</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16881,8 +17711,181 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118727557</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>